--- a/spots_en.xlsx
+++ b/spots_en.xlsx
@@ -601,7 +601,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>観光地</t>
+          <t>文化</t>
         </is>
       </c>
       <c r="D6" t="n">
@@ -663,7 +663,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>観光地</t>
+          <t>公園</t>
         </is>
       </c>
       <c r="D8" t="n">
@@ -725,7 +725,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>観光地</t>
+          <t>自然</t>
         </is>
       </c>
       <c r="D10" t="n">
@@ -756,7 +756,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>観光地</t>
+          <t>公園</t>
         </is>
       </c>
       <c r="D11" t="n">
@@ -787,7 +787,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>観光地</t>
+          <t>自然</t>
         </is>
       </c>
       <c r="D12" t="n">
@@ -818,7 +818,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>観光地</t>
+          <t>自然</t>
         </is>
       </c>
       <c r="D13" t="n">
@@ -849,7 +849,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>観光地</t>
+          <t>進撃の巨人</t>
         </is>
       </c>
       <c r="D14" t="n">
@@ -1004,7 +1004,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>観光地</t>
+          <t>公園</t>
         </is>
       </c>
       <c r="D19" t="n">
@@ -1035,7 +1035,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>観光地</t>
+          <t>公園</t>
         </is>
       </c>
       <c r="D20" t="n">
@@ -1438,7 +1438,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>観光地</t>
+          <t>体験</t>
         </is>
       </c>
       <c r="D33" t="n">
@@ -1965,7 +1965,7 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>観光地</t>
+          <t>歴史</t>
         </is>
       </c>
       <c r="D50" t="n">

--- a/spots_en.xlsx
+++ b/spots_en.xlsx
@@ -7,7 +7,8 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="観光" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="防災" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -1987,4 +1988,5194 @@
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:J123"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>スポット名</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>カテゴリ</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>緯度</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>経度</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>所要時間（参考）</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>説明</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>収容人数</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>状態</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>所要時間</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>1</v>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>亀山公園</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>指定緊急避難場所</t>
+        </is>
+      </c>
+      <c r="D2" t="n">
+        <v>33.314202</v>
+      </c>
+      <c r="E2" t="n">
+        <v>130.928977</v>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>5分</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>【種別：指定緊急避難場所】【対応災害：地震】【所在地：大分県日田市中ノ島町559】</t>
+        </is>
+      </c>
+      <c r="H2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>待機中</t>
+        </is>
+      </c>
+      <c r="J2" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>2</v>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>三隈川公園</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>指定緊急避難場所</t>
+        </is>
+      </c>
+      <c r="D3" t="n">
+        <v>33.312586</v>
+      </c>
+      <c r="E3" t="n">
+        <v>130.926251</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>5分</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>【種別：指定緊急避難場所】【対応災害：地震】【所在地：大分県日田市中ノ島町608-3】</t>
+        </is>
+      </c>
+      <c r="H3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>待機中</t>
+        </is>
+      </c>
+      <c r="J3" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>3</v>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>老人福祉センター延寿グラウンド</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>指定緊急避難場所</t>
+        </is>
+      </c>
+      <c r="D4" t="n">
+        <v>33.311526</v>
+      </c>
+      <c r="E4" t="n">
+        <v>130.918487</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>5分</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>【種別：指定緊急避難場所】【対応災害：地震】【所在地：大分県日田市中ノ島町685-13】【連絡先：(0973)24-2123】</t>
+        </is>
+      </c>
+      <c r="H4" t="n">
+        <v>0</v>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>待機中</t>
+        </is>
+      </c>
+      <c r="J4" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>4</v>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>本町第一公園</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>指定緊急避難場所</t>
+        </is>
+      </c>
+      <c r="D5" t="n">
+        <v>33.316442</v>
+      </c>
+      <c r="E5" t="n">
+        <v>130.935914</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>5分</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>【種別：指定緊急避難場所】【対応災害：地震】【所在地：大分県日田市本町19】</t>
+        </is>
+      </c>
+      <c r="H5" t="n">
+        <v>0</v>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>待機中</t>
+        </is>
+      </c>
+      <c r="J5" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>5</v>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>本町第二公園</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>指定緊急避難場所</t>
+        </is>
+      </c>
+      <c r="D6" t="n">
+        <v>33.315288</v>
+      </c>
+      <c r="E6" t="n">
+        <v>130.937311</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>5分</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>【種別：指定緊急避難場所】【対応災害：地震】【所在地：大分県日田市本町56】</t>
+        </is>
+      </c>
+      <c r="H6" t="n">
+        <v>0</v>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>待機中</t>
+        </is>
+      </c>
+      <c r="J6" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>6</v>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>東町児童公園</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>指定緊急避難場所</t>
+        </is>
+      </c>
+      <c r="D7" t="n">
+        <v>33.312077</v>
+      </c>
+      <c r="E7" t="n">
+        <v>130.935111</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>5分</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>【種別：指定緊急避難場所】【対応災害：地震】【所在地：大分県日田市東町716-3】</t>
+        </is>
+      </c>
+      <c r="H7" t="n">
+        <v>0</v>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>待機中</t>
+        </is>
+      </c>
+      <c r="J7" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>7</v>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>竹田公園</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>指定緊急避難場所</t>
+        </is>
+      </c>
+      <c r="D8" t="n">
+        <v>33.308589</v>
+      </c>
+      <c r="E8" t="n">
+        <v>130.939109</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>5分</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>【種別：指定緊急避難場所】【対応災害：地震】【所在地：大分県日田市若宮町1233-4】</t>
+        </is>
+      </c>
+      <c r="H8" t="n">
+        <v>0</v>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>待機中</t>
+        </is>
+      </c>
+      <c r="J8" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>8</v>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>南元町児童公園</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>指定緊急避難場所</t>
+        </is>
+      </c>
+      <c r="D9" t="n">
+        <v>33.31354</v>
+      </c>
+      <c r="E9" t="n">
+        <v>130.940083</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>5分</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>【種別：指定緊急避難場所】【対応災害：地震】【所在地：大分県日田市南元町132】</t>
+        </is>
+      </c>
+      <c r="H9" t="n">
+        <v>0</v>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>待機中</t>
+        </is>
+      </c>
+      <c r="J9" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>9</v>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>港町児童公園</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>指定緊急避難場所</t>
+        </is>
+      </c>
+      <c r="D10" t="n">
+        <v>33.325351</v>
+      </c>
+      <c r="E10" t="n">
+        <v>130.936197</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>5分</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>【種別：指定緊急避難場所】【対応災害：地震】【所在地：大分県日田市港町398-5】</t>
+        </is>
+      </c>
+      <c r="H10" t="n">
+        <v>0</v>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>待機中</t>
+        </is>
+      </c>
+      <c r="J10" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>10</v>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>中城グラウンド</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>指定緊急避難場所</t>
+        </is>
+      </c>
+      <c r="D11" t="n">
+        <v>33.325109</v>
+      </c>
+      <c r="E11" t="n">
+        <v>130.940601</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>5分</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>【種別：指定緊急避難場所】【対応災害：地震】【所在地：大分県日田市中城町224-1】</t>
+        </is>
+      </c>
+      <c r="H11" t="n">
+        <v>0</v>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>待機中</t>
+        </is>
+      </c>
+      <c r="J11" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>11</v>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>桂林荘（城町第一児童）公園</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>指定緊急避難場所</t>
+        </is>
+      </c>
+      <c r="D12" t="n">
+        <v>33.327262</v>
+      </c>
+      <c r="E12" t="n">
+        <v>130.938944</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>5分</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>【種別：指定緊急避難場所】【対応災害：地震】【所在地：大分県日田市城町一丁目305-1】</t>
+        </is>
+      </c>
+      <c r="H12" t="n">
+        <v>0</v>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>待機中</t>
+        </is>
+      </c>
+      <c r="J12" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>12</v>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>月隈公園</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>指定緊急避難場所</t>
+        </is>
+      </c>
+      <c r="D13" t="n">
+        <v>33.331672</v>
+      </c>
+      <c r="E13" t="n">
+        <v>130.936257</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>5分</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>【種別：指定緊急避難場所】【対応災害：地震】【所在地：大分県日田市丸山二丁目2-1】</t>
+        </is>
+      </c>
+      <c r="H13" t="n">
+        <v>0</v>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>待機中</t>
+        </is>
+      </c>
+      <c r="J13" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>13</v>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>田島第一児童公園</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>指定緊急避難場所</t>
+        </is>
+      </c>
+      <c r="D14" t="n">
+        <v>33.317445</v>
+      </c>
+      <c r="E14" t="n">
+        <v>130.941412</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>5分</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>【種別：指定緊急避難場所】【対応災害：地震】【所在地：大分県日田市田島一丁目143】</t>
+        </is>
+      </c>
+      <c r="H14" t="n">
+        <v>0</v>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>待機中</t>
+        </is>
+      </c>
+      <c r="J14" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>14</v>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>田島第二児童公園</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>指定緊急避難場所</t>
+        </is>
+      </c>
+      <c r="D15" t="n">
+        <v>33.319808</v>
+      </c>
+      <c r="E15" t="n">
+        <v>130.941894</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>5分</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>【種別：指定緊急避難場所】【対応災害：地震】【所在地：大分県日田市田島二丁目286】</t>
+        </is>
+      </c>
+      <c r="H15" t="n">
+        <v>0</v>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>待機中</t>
+        </is>
+      </c>
+      <c r="J15" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>15</v>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>田島第三児童公園</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>指定緊急避難場所</t>
+        </is>
+      </c>
+      <c r="D16" t="n">
+        <v>33.315038</v>
+      </c>
+      <c r="E16" t="n">
+        <v>130.942466</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>5分</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>【種別：指定緊急避難場所】【対応災害：地震】【所在地：大分県日田市田島一丁目606】</t>
+        </is>
+      </c>
+      <c r="H16" t="n">
+        <v>0</v>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>待機中</t>
+        </is>
+      </c>
+      <c r="J16" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>16</v>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>田島本町児童公園</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>指定緊急避難場所</t>
+        </is>
+      </c>
+      <c r="D17" t="n">
+        <v>33.31923</v>
+      </c>
+      <c r="E17" t="n">
+        <v>130.939198</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>5分</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>【種別：指定緊急避難場所】【対応災害：地震】【所在地：大分県日田市田島本町175】</t>
+        </is>
+      </c>
+      <c r="H17" t="n">
+        <v>0</v>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>待機中</t>
+        </is>
+      </c>
+      <c r="J17" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>17</v>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>三芳児童公園</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>指定緊急避難場所</t>
+        </is>
+      </c>
+      <c r="D18" t="n">
+        <v>33.306132</v>
+      </c>
+      <c r="E18" t="n">
+        <v>130.948282</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>5分</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>【種別：指定緊急避難場所】【対応災害：地震】【所在地：大分県日田市下井手町20】</t>
+        </is>
+      </c>
+      <c r="H18" t="n">
+        <v>0</v>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>待機中</t>
+        </is>
+      </c>
+      <c r="J18" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>18</v>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>小渕児童公園</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>指定緊急避難場所</t>
+        </is>
+      </c>
+      <c r="D19" t="n">
+        <v>33.304518</v>
+      </c>
+      <c r="E19" t="n">
+        <v>130.948433</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>5分</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>【種別：指定緊急避難場所】【対応災害：地震】【所在地：大分県日田市三芳小渕町73】</t>
+        </is>
+      </c>
+      <c r="H19" t="n">
+        <v>0</v>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>待機中</t>
+        </is>
+      </c>
+      <c r="J19" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>19</v>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>京町公園</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>指定緊急避難場所</t>
+        </is>
+      </c>
+      <c r="D20" t="n">
+        <v>33.310135</v>
+      </c>
+      <c r="E20" t="n">
+        <v>130.928562</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>5分</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>【種別：指定緊急避難場所】【対応災害：地震】【所在地：大分県日田市京町27-1】</t>
+        </is>
+      </c>
+      <c r="H20" t="n">
+        <v>0</v>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>待機中</t>
+        </is>
+      </c>
+      <c r="J20" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>20</v>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>鏡坂公園</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>指定緊急避難場所</t>
+        </is>
+      </c>
+      <c r="D21" t="n">
+        <v>33.309338</v>
+      </c>
+      <c r="E21" t="n">
+        <v>130.923827</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>5分</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>【種別：指定緊急避難場所】【対応災害：地震】【所在地：大分県日田市上野町393-1】</t>
+        </is>
+      </c>
+      <c r="H21" t="n">
+        <v>0</v>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>待機中</t>
+        </is>
+      </c>
+      <c r="J21" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>21</v>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>平野球場</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>指定緊急避難場所</t>
+        </is>
+      </c>
+      <c r="D22" t="n">
+        <v>33.295358</v>
+      </c>
+      <c r="E22" t="n">
+        <v>130.906143</v>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>5分</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>【種別：指定緊急避難場所】【対応災害：地震】【所在地：大分県日田市小山479-1】</t>
+        </is>
+      </c>
+      <c r="H22" t="n">
+        <v>0</v>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>待機中</t>
+        </is>
+      </c>
+      <c r="J22" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>22</v>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>星隈公園</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>指定緊急避難場所</t>
+        </is>
+      </c>
+      <c r="D23" t="n">
+        <v>33.325584</v>
+      </c>
+      <c r="E23" t="n">
+        <v>130.90538</v>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>5分</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>【種別：指定緊急避難場所】【対応災害：地震】【所在地：大分県日田市北友田二丁目1950-1】</t>
+        </is>
+      </c>
+      <c r="H23" t="n">
+        <v>0</v>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>待機中</t>
+        </is>
+      </c>
+      <c r="J23" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>23</v>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>北友田三丁目児童公園</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>指定緊急避難場所</t>
+        </is>
+      </c>
+      <c r="D24" t="n">
+        <v>33.322929</v>
+      </c>
+      <c r="E24" t="n">
+        <v>130.900722</v>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>5分</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>【種別：指定緊急避難場所】【対応災害：地震】【所在地：大分県日田市北友田三丁目2531-37】</t>
+        </is>
+      </c>
+      <c r="H24" t="n">
+        <v>0</v>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>待機中</t>
+        </is>
+      </c>
+      <c r="J24" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>24</v>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>光岡スポーツ広場</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>指定緊急避難場所</t>
+        </is>
+      </c>
+      <c r="D25" t="n">
+        <v>33.327623</v>
+      </c>
+      <c r="E25" t="n">
+        <v>130.896269</v>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>5分</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>【種別：指定緊急避難場所】【対応災害：地震】【所在地：大分県日田市友田2483-3】</t>
+        </is>
+      </c>
+      <c r="H25" t="n">
+        <v>0</v>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>待機中</t>
+        </is>
+      </c>
+      <c r="J25" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>25</v>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>萩尾公園</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>指定緊急避難場所</t>
+        </is>
+      </c>
+      <c r="D26" t="n">
+        <v>33.330735</v>
+      </c>
+      <c r="E26" t="n">
+        <v>130.887468</v>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>5分</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>【種別：指定緊急避難場所】【対応災害：地震】【所在地：大分県日田市君迫町1335-1】</t>
+        </is>
+      </c>
+      <c r="H26" t="n">
+        <v>0</v>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>待機中</t>
+        </is>
+      </c>
+      <c r="J26" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>26</v>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>朝日ヶ丘球場</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>指定緊急避難場所</t>
+        </is>
+      </c>
+      <c r="D27" t="n">
+        <v>33.331083</v>
+      </c>
+      <c r="E27" t="n">
+        <v>130.916267</v>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>5分</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>【種別：指定緊急避難場所】【対応災害：地震】【所在地：大分県日田市北友田1丁目1544-3】</t>
+        </is>
+      </c>
+      <c r="H27" t="n">
+        <v>0</v>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>待機中</t>
+        </is>
+      </c>
+      <c r="J27" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>27</v>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>三和スポーツ広場</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>指定緊急避難場所</t>
+        </is>
+      </c>
+      <c r="D28" t="n">
+        <v>33.351501</v>
+      </c>
+      <c r="E28" t="n">
+        <v>130.936855</v>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>5分</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>【種別：指定緊急避難場所】【対応災害：地震】【所在地：大分県日田市清水町1823-1】</t>
+        </is>
+      </c>
+      <c r="H28" t="n">
+        <v>0</v>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>待機中</t>
+        </is>
+      </c>
+      <c r="J28" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>28</v>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>財津町スポーツ広場</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>指定緊急避難場所</t>
+        </is>
+      </c>
+      <c r="D29" t="n">
+        <v>33.353547</v>
+      </c>
+      <c r="E29" t="n">
+        <v>130.95435</v>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>5分</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>【種別：指定緊急避難場所】【対応災害：地震】【所在地：大分県日田市財津町2688-2】</t>
+        </is>
+      </c>
+      <c r="H29" t="n">
+        <v>0</v>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>待機中</t>
+        </is>
+      </c>
+      <c r="J29" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>29</v>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>旧北小野小学校グラウンド</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>指定緊急避難場所</t>
+        </is>
+      </c>
+      <c r="D30" t="n">
+        <v>33.404527</v>
+      </c>
+      <c r="E30" t="n">
+        <v>130.937084</v>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>5分</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>【種別：指定緊急避難場所】【対応災害：地震】【所在地：大分県日田市殿町3850-3】</t>
+        </is>
+      </c>
+      <c r="H30" t="n">
+        <v>0</v>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>待機中</t>
+        </is>
+      </c>
+      <c r="J30" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>30</v>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>東有田スポーツ広場</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>指定緊急避難場所</t>
+        </is>
+      </c>
+      <c r="D31" t="n">
+        <v>33.331172</v>
+      </c>
+      <c r="E31" t="n">
+        <v>130.979257</v>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>5分</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>【種別：指定緊急避難場所】【対応災害：地震】【所在地：大分県日田市諸留町51】</t>
+        </is>
+      </c>
+      <c r="H31" t="n">
+        <v>0</v>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>待機中</t>
+        </is>
+      </c>
+      <c r="J31" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>31</v>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>大鶴スポーツ広場</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>指定緊急避難場所</t>
+        </is>
+      </c>
+      <c r="D32" t="n">
+        <v>33.370811</v>
+      </c>
+      <c r="E32" t="n">
+        <v>130.890985</v>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>5分</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>【種別：指定緊急避難場所】【対応災害：地震】【所在地：大分県日田市大鶴本町884-1】</t>
+        </is>
+      </c>
+      <c r="H32" t="n">
+        <v>0</v>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>待機中</t>
+        </is>
+      </c>
+      <c r="J32" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="n">
+        <v>32</v>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>旧大野小学校グラウンド</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>指定緊急避難場所</t>
+        </is>
+      </c>
+      <c r="D33" t="n">
+        <v>33.210929</v>
+      </c>
+      <c r="E33" t="n">
+        <v>130.916252</v>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>5分</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>【種別：指定緊急避難場所】【対応災害：地震】【所在地：大分県日田市前津江町大野2230-2】</t>
+        </is>
+      </c>
+      <c r="H33" t="n">
+        <v>0</v>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>待機中</t>
+        </is>
+      </c>
+      <c r="J33" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="n">
+        <v>33</v>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>上野田多目的スポーツ広場</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>指定緊急避難場所</t>
+        </is>
+      </c>
+      <c r="D34" t="n">
+        <v>33.088651</v>
+      </c>
+      <c r="E34" t="n">
+        <v>130.986535</v>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>5分</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>【種別：指定緊急避難場所】【対応災害：地震】【所在地：大分県日田市上津江町上野田68-2】</t>
+        </is>
+      </c>
+      <c r="H34" t="n">
+        <v>0</v>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>待機中</t>
+        </is>
+      </c>
+      <c r="J34" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="n">
+        <v>34</v>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>旧松原小学校グラウンド</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>指定緊急避難場所</t>
+        </is>
+      </c>
+      <c r="D35" t="n">
+        <v>33.198324</v>
+      </c>
+      <c r="E35" t="n">
+        <v>130.991979</v>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>5分</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>【種別：指定緊急避難場所】【対応災害：地震】【所在地：大分県日田市大山町西大山8344-2】</t>
+        </is>
+      </c>
+      <c r="H35" t="n">
+        <v>0</v>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>待機中</t>
+        </is>
+      </c>
+      <c r="J35" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="n">
+        <v>35</v>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>咸宜小学校</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>指定避難所</t>
+        </is>
+      </c>
+      <c r="D36" t="n">
+        <v>33.321636</v>
+      </c>
+      <c r="E36" t="n">
+        <v>130.936576</v>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>5分</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>【種別：指定避難所】【対応災害：洪水, 崖崩れ・土石流, 地震】【所在地：大分県日田市淡窓一丁目5-13】【連絡先：(0973)23-6292】</t>
+        </is>
+      </c>
+      <c r="H36" t="n">
+        <v>0</v>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>待機中</t>
+        </is>
+      </c>
+      <c r="J36" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="n">
+        <v>36</v>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>咸宜公民館</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>指定避難所</t>
+        </is>
+      </c>
+      <c r="D37" t="n">
+        <v>33.322177</v>
+      </c>
+      <c r="E37" t="n">
+        <v>130.936608</v>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>5分</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>【種別：指定避難所】【対応災害：洪水, 崖崩れ・土石流, 地震】【所在地：大分県日田市淡窓一丁目5-31】【連絡先：(0973)22-5191】</t>
+        </is>
+      </c>
+      <c r="H37" t="n">
+        <v>0</v>
+      </c>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>待機中</t>
+        </is>
+      </c>
+      <c r="J37" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="n">
+        <v>37</v>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>市民文化会館（パトリア日田）</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>指定避難所</t>
+        </is>
+      </c>
+      <c r="D38" t="n">
+        <v>33.319326</v>
+      </c>
+      <c r="E38" t="n">
+        <v>130.93429</v>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>5分</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>【種別：指定避難所】【対応災害：洪水, 崖崩れ・土石流, 地震】【所在地：大分県日田市三本松一丁目8番11号】【連絡先：(0973)25-5000】</t>
+        </is>
+      </c>
+      <c r="H38" t="n">
+        <v>0</v>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>待機中</t>
+        </is>
+      </c>
+      <c r="J38" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="n">
+        <v>38</v>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>桂林小学校</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>指定避難所</t>
+        </is>
+      </c>
+      <c r="D39" t="n">
+        <v>33.326544</v>
+      </c>
+      <c r="E39" t="n">
+        <v>130.942727</v>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>5分</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>【種別：指定避難所】【対応災害：洪水, 崖崩れ・土石流, 地震】【所在地：大分県日田市上城内町2-35】【連絡先：(0973)24-6081】</t>
+        </is>
+      </c>
+      <c r="H39" t="n">
+        <v>0</v>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>待機中</t>
+        </is>
+      </c>
+      <c r="J39" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="n">
+        <v>39</v>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>中央公民館</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>指定避難所</t>
+        </is>
+      </c>
+      <c r="D40" t="n">
+        <v>33.325985</v>
+      </c>
+      <c r="E40" t="n">
+        <v>130.941879</v>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>5分</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>【種別：指定避難所】【対応災害：洪水, 崖崩れ・土石流, 地震】【所在地：大分県日田市上城内町2-6】【連絡先：(0973)22-6868】</t>
+        </is>
+      </c>
+      <c r="H40" t="n">
+        <v>0</v>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>待機中</t>
+        </is>
+      </c>
+      <c r="J40" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="n">
+        <v>40</v>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>桂林公民館</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>指定避難所</t>
+        </is>
+      </c>
+      <c r="D41" t="n">
+        <v>33.326111</v>
+      </c>
+      <c r="E41" t="n">
+        <v>130.942889</v>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>5分</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>【種別：指定避難所】【対応災害：洪水, 崖崩れ・土石流, 地震】【所在地：大分県日田市上城内町2-11】【連絡先：(0973)24-3131】</t>
+        </is>
+      </c>
+      <c r="H41" t="n">
+        <v>0</v>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>待機中</t>
+        </is>
+      </c>
+      <c r="J41" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="n">
+        <v>41</v>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>東部中学校</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>指定避難所</t>
+        </is>
+      </c>
+      <c r="D42" t="n">
+        <v>33.317708</v>
+      </c>
+      <c r="E42" t="n">
+        <v>130.943936</v>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>5分</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>【種別：指定避難所】【対応災害：洪水, 崖崩れ・土石流, 地震】【所在地：大分県日田市田島二丁目12-8】【連絡先：(0973)22-7135】</t>
+        </is>
+      </c>
+      <c r="H42" t="n">
+        <v>0</v>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>待機中</t>
+        </is>
+      </c>
+      <c r="J42" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="n">
+        <v>42</v>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>大分県立日田高等学校</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>指定避難所</t>
+        </is>
+      </c>
+      <c r="D43" t="n">
+        <v>33.322532</v>
+      </c>
+      <c r="E43" t="n">
+        <v>130.943224</v>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>5分</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>【種別：指定避難所】【対応災害：洪水, 崖崩れ・土石流, 地震】【所在地：大分県日田市田島二丁目9-30】【連絡先：(0973)23-0166】</t>
+        </is>
+      </c>
+      <c r="H43" t="n">
+        <v>0</v>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>待機中</t>
+        </is>
+      </c>
+      <c r="J43" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="n">
+        <v>43</v>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>藤蔭高等学校</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>指定避難所</t>
+        </is>
+      </c>
+      <c r="D44" t="n">
+        <v>33.319843</v>
+      </c>
+      <c r="E44" t="n">
+        <v>130.939928</v>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>5分</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>【種別：指定避難所】【対応災害：洪水, 崖崩れ・土石流, 地震】【所在地：大分県日田市田島本町5-41】【連絡先：(0973)24-2737】</t>
+        </is>
+      </c>
+      <c r="H44" t="n">
+        <v>0</v>
+      </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>待機中</t>
+        </is>
+      </c>
+      <c r="J44" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="n">
+        <v>44</v>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>ＳＷＳ西日本アリーナ日田（日田市総合体育館）</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>指定避難所</t>
+        </is>
+      </c>
+      <c r="D45" t="n">
+        <v>33.318829</v>
+      </c>
+      <c r="E45" t="n">
+        <v>130.951045</v>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>5分</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>【種別：指定避難所】【対応災害：洪水, 崖崩れ・土石流, 地震】【所在地：大分県日田市田島三丁目29】【連絡先：(0973)24-6750】</t>
+        </is>
+      </c>
+      <c r="H45" t="n">
+        <v>0</v>
+      </c>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>待機中</t>
+        </is>
+      </c>
+      <c r="J45" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="n">
+        <v>45</v>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>勤労者総合福祉センター（サンヒルズひた）</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>指定避難所</t>
+        </is>
+      </c>
+      <c r="D46" t="n">
+        <v>33.320596</v>
+      </c>
+      <c r="E46" t="n">
+        <v>130.951076</v>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>5分</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>【種別：指定避難所】【対応災害：洪水, 崖崩れ・土石流, 地震】【所在地：大分県日田市田島三丁目69】【連絡先：(0973)22-5733】</t>
+        </is>
+      </c>
+      <c r="H46" t="n">
+        <v>0</v>
+      </c>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>待機中</t>
+        </is>
+      </c>
+      <c r="J46" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="n">
+        <v>46</v>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>日隈小学校</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>指定避難所</t>
+        </is>
+      </c>
+      <c r="D47" t="n">
+        <v>33.315002</v>
+      </c>
+      <c r="E47" t="n">
+        <v>130.926013</v>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>5分</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>【種別：指定避難所】【対応災害：崖崩れ・土石流, 地震】【所在地：大分県日田市日ノ隈町578-1】【連絡先：(0973)23-6285】</t>
+        </is>
+      </c>
+      <c r="H47" t="n">
+        <v>0</v>
+      </c>
+      <c r="I47" t="inlineStr">
+        <is>
+          <t>待機中</t>
+        </is>
+      </c>
+      <c r="J47" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="n">
+        <v>47</v>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>日隈公民館</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>指定避難所</t>
+        </is>
+      </c>
+      <c r="D48" t="n">
+        <v>33.315416</v>
+      </c>
+      <c r="E48" t="n">
+        <v>130.924101</v>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>5分</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>【種別：指定避難所】【対応災害：洪水, 崖崩れ・土石流, 地震】【所在地：大分県日田市日ノ隈町515-1】【連絡先：(0973)22-6982】</t>
+        </is>
+      </c>
+      <c r="H48" t="n">
+        <v>0</v>
+      </c>
+      <c r="I48" t="inlineStr">
+        <is>
+          <t>待機中</t>
+        </is>
+      </c>
+      <c r="J48" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="n">
+        <v>48</v>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>三隈中学校</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>指定避難所</t>
+        </is>
+      </c>
+      <c r="D49" t="n">
+        <v>33.315456</v>
+      </c>
+      <c r="E49" t="n">
+        <v>130.915476</v>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>5分</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>【種別：指定避難所】【対応災害：崖崩れ・土石流, 地震】【所在地：大分県日田市亀川町402-1】【連絡先：(0973)23-6237】</t>
+        </is>
+      </c>
+      <c r="H49" t="n">
+        <v>0</v>
+      </c>
+      <c r="I49" t="inlineStr">
+        <is>
+          <t>待機中</t>
+        </is>
+      </c>
+      <c r="J49" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="n">
+        <v>49</v>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>若宮小学校</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>指定避難所</t>
+        </is>
+      </c>
+      <c r="D50" t="n">
+        <v>33.31042</v>
+      </c>
+      <c r="E50" t="n">
+        <v>130.939376</v>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>5分</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>【種別：指定避難所】【対応災害：崖崩れ・土石流, 地震】【所在地：大分県日田市若宮町2-15】【連絡先：(0973)23-6282】</t>
+        </is>
+      </c>
+      <c r="H50" t="n">
+        <v>0</v>
+      </c>
+      <c r="I50" t="inlineStr">
+        <is>
+          <t>待機中</t>
+        </is>
+      </c>
+      <c r="J50" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="n">
+        <v>50</v>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>若宮公民館</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>指定避難所</t>
+        </is>
+      </c>
+      <c r="D51" t="n">
+        <v>33.312872</v>
+      </c>
+      <c r="E51" t="n">
+        <v>130.938365</v>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>5分</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>【種別：指定避難所】【対応災害：洪水, 崖崩れ・土石流, 地震】【所在地：大分県日田市竹田新町1-37】【連絡先：(0973)23-9850】</t>
+        </is>
+      </c>
+      <c r="H51" t="n">
+        <v>0</v>
+      </c>
+      <c r="I51" t="inlineStr">
+        <is>
+          <t>待機中</t>
+        </is>
+      </c>
+      <c r="J51" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="n">
+        <v>51</v>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>三芳公民館</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>指定避難所</t>
+        </is>
+      </c>
+      <c r="D52" t="n">
+        <v>33.30706</v>
+      </c>
+      <c r="E52" t="n">
+        <v>130.947197</v>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>5分</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>【種別：指定避難所】【対応災害：崖崩れ・土石流, 地震】【所在地：大分県日田市下井手町989】【連絡先：(0973)22-1491】</t>
+        </is>
+      </c>
+      <c r="H52" t="n">
+        <v>0</v>
+      </c>
+      <c r="I52" t="inlineStr">
+        <is>
+          <t>待機中</t>
+        </is>
+      </c>
+      <c r="J52" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="n">
+        <v>52</v>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>三芳小学校</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>指定避難所</t>
+        </is>
+      </c>
+      <c r="D53" t="n">
+        <v>33.307763</v>
+      </c>
+      <c r="E53" t="n">
+        <v>130.946627</v>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>5分</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>【種別：指定避難所】【対応災害：崖崩れ・土石流, 地震】【所在地：大分県日田市下井手町940】【連絡先：(0973)23-6234】</t>
+        </is>
+      </c>
+      <c r="H53" t="n">
+        <v>0</v>
+      </c>
+      <c r="I53" t="inlineStr">
+        <is>
+          <t>待機中</t>
+        </is>
+      </c>
+      <c r="J53" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="n">
+        <v>53</v>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>南部中学校</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>指定避難所</t>
+        </is>
+      </c>
+      <c r="D54" t="n">
+        <v>33.307232</v>
+      </c>
+      <c r="E54" t="n">
+        <v>130.93112</v>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>5分</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>【種別：指定避難所】【対応災害：洪水, 崖崩れ・土石流, 地震】【所在地：大分県日田市銭渕町288】【連絡先：(0973)23-6275】</t>
+        </is>
+      </c>
+      <c r="H54" t="n">
+        <v>0</v>
+      </c>
+      <c r="I54" t="inlineStr">
+        <is>
+          <t>待機中</t>
+        </is>
+      </c>
+      <c r="J54" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="n">
+        <v>54</v>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>高瀬小学校</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>指定避難所</t>
+        </is>
+      </c>
+      <c r="D55" t="n">
+        <v>33.301428</v>
+      </c>
+      <c r="E55" t="n">
+        <v>130.936988</v>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>5分</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>【種別：指定避難所】【対応災害：洪水, 崖崩れ・土石流, 地震】【所在地：大分県日田市誠和町781-2】【連絡先：(0973)23-6241】</t>
+        </is>
+      </c>
+      <c r="H55" t="n">
+        <v>0</v>
+      </c>
+      <c r="I55" t="inlineStr">
+        <is>
+          <t>待機中</t>
+        </is>
+      </c>
+      <c r="J55" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="n">
+        <v>55</v>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>高瀬公民館</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>指定避難所</t>
+        </is>
+      </c>
+      <c r="D56" t="n">
+        <v>33.302069</v>
+      </c>
+      <c r="E56" t="n">
+        <v>130.936654</v>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>5分</t>
+        </is>
+      </c>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>【種別：指定避難所】【対応災害：洪水, 崖崩れ・土石流, 地震】【所在地：大分県日田市誠和町796-3】【連絡先：(0973)24-2705】</t>
+        </is>
+      </c>
+      <c r="H56" t="n">
+        <v>0</v>
+      </c>
+      <c r="I56" t="inlineStr">
+        <is>
+          <t>待機中</t>
+        </is>
+      </c>
+      <c r="J56" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="n">
+        <v>56</v>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>大分県立日田林工高等学校</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>指定避難所</t>
+        </is>
+      </c>
+      <c r="D57" t="n">
+        <v>33.331427</v>
+      </c>
+      <c r="E57" t="n">
+        <v>130.934216</v>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>5分</t>
+        </is>
+      </c>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>【種別：指定避難所】【対応災害：崖崩れ・土石流, 地震】【所在地：大分県日田市吹上町30】【連絡先：(0973)22-5171】</t>
+        </is>
+      </c>
+      <c r="H57" t="n">
+        <v>0</v>
+      </c>
+      <c r="I57" t="inlineStr">
+        <is>
+          <t>待機中</t>
+        </is>
+      </c>
+      <c r="J57" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="n">
+        <v>57</v>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>光岡小学校</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>指定避難所</t>
+        </is>
+      </c>
+      <c r="D58" t="n">
+        <v>33.327922</v>
+      </c>
+      <c r="E58" t="n">
+        <v>130.922994</v>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>5分</t>
+        </is>
+      </c>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>【種別：指定避難所】【対応災害：地震】【所在地：大分県日田市北友田一丁目1133-2】【連絡先：(0973)23-6258】</t>
+        </is>
+      </c>
+      <c r="H58" t="n">
+        <v>0</v>
+      </c>
+      <c r="I58" t="inlineStr">
+        <is>
+          <t>待機中</t>
+        </is>
+      </c>
+      <c r="J58" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="n">
+        <v>58</v>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>光岡公民館</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>指定避難所</t>
+        </is>
+      </c>
+      <c r="D59" t="n">
+        <v>33.328282</v>
+      </c>
+      <c r="E59" t="n">
+        <v>130.92192</v>
+      </c>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>5分</t>
+        </is>
+      </c>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>【種別：指定避難所】【対応災害：崖崩れ・土石流, 地震】【所在地：大分県日田市北友田一丁目1221-1】【連絡先：(0973)23-8984】</t>
+        </is>
+      </c>
+      <c r="H59" t="n">
+        <v>0</v>
+      </c>
+      <c r="I59" t="inlineStr">
+        <is>
+          <t>待機中</t>
+        </is>
+      </c>
+      <c r="J59" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="n">
+        <v>59</v>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>大分県立日田三隈高等学校</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>指定避難所</t>
+        </is>
+      </c>
+      <c r="D60" t="n">
+        <v>33.331163</v>
+      </c>
+      <c r="E60" t="n">
+        <v>130.914645</v>
+      </c>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>5分</t>
+        </is>
+      </c>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>【種別：指定避難所】【対応災害：洪水, 崖崩れ・土石流, 地震】【所在地：大分県日田市友田1546-1】【連絡先：(0973)23-3130】</t>
+        </is>
+      </c>
+      <c r="H60" t="n">
+        <v>0</v>
+      </c>
+      <c r="I60" t="inlineStr">
+        <is>
+          <t>待機中</t>
+        </is>
+      </c>
+      <c r="J60" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="n">
+        <v>60</v>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>浄化センター</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>指定避難所</t>
+        </is>
+      </c>
+      <c r="D61" t="n">
+        <v>33.322366</v>
+      </c>
+      <c r="E61" t="n">
+        <v>130.90706</v>
+      </c>
+      <c r="F61" t="inlineStr">
+        <is>
+          <t>5分</t>
+        </is>
+      </c>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>【種別：指定避難所】【対応災害：崖崩れ・土石流, 地震】【所在地：大分県日田市南友田町717-1】【連絡先：(0973)24-3350】</t>
+        </is>
+      </c>
+      <c r="H61" t="n">
+        <v>0</v>
+      </c>
+      <c r="I61" t="inlineStr">
+        <is>
+          <t>待機中</t>
+        </is>
+      </c>
+      <c r="J61" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="n">
+        <v>61</v>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>昭和学園高等学校</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>指定避難所</t>
+        </is>
+      </c>
+      <c r="D62" t="n">
+        <v>33.33341</v>
+      </c>
+      <c r="E62" t="n">
+        <v>130.940649</v>
+      </c>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>5分</t>
+        </is>
+      </c>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>【種別：指定避難所】【対応災害：崖崩れ・土石流, 地震】【所在地：大分県日田市日ノ出町14】【連絡先：(0973)22-7420】</t>
+        </is>
+      </c>
+      <c r="H62" t="n">
+        <v>0</v>
+      </c>
+      <c r="I62" t="inlineStr">
+        <is>
+          <t>待機中</t>
+        </is>
+      </c>
+      <c r="J62" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="n">
+        <v>62</v>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>朝日小学校</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>指定避難所</t>
+        </is>
+      </c>
+      <c r="D63" t="n">
+        <v>33.341581</v>
+      </c>
+      <c r="E63" t="n">
+        <v>130.919147</v>
+      </c>
+      <c r="F63" t="inlineStr">
+        <is>
+          <t>5分</t>
+        </is>
+      </c>
+      <c r="G63" t="inlineStr">
+        <is>
+          <t>【種別：指定避難所】【対応災害：洪水, 崖崩れ・土石流, 地震】【所在地：大分県日田市朝日町936-1】【連絡先：(0973)22-5242】</t>
+        </is>
+      </c>
+      <c r="H63" t="n">
+        <v>0</v>
+      </c>
+      <c r="I63" t="inlineStr">
+        <is>
+          <t>待機中</t>
+        </is>
+      </c>
+      <c r="J63" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="n">
+        <v>63</v>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>朝日公民館</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>指定避難所</t>
+        </is>
+      </c>
+      <c r="D64" t="n">
+        <v>33.340995</v>
+      </c>
+      <c r="E64" t="n">
+        <v>130.919448</v>
+      </c>
+      <c r="F64" t="inlineStr">
+        <is>
+          <t>5分</t>
+        </is>
+      </c>
+      <c r="G64" t="inlineStr">
+        <is>
+          <t>【種別：指定避難所】【対応災害：洪水, 崖崩れ・土石流, 地震】【所在地：大分県日田市朝日町945-1】【連絡先：(0973)23-8994】</t>
+        </is>
+      </c>
+      <c r="H64" t="n">
+        <v>0</v>
+      </c>
+      <c r="I64" t="inlineStr">
+        <is>
+          <t>待機中</t>
+        </is>
+      </c>
+      <c r="J64" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="n">
+        <v>64</v>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>三和小学校</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>指定避難所</t>
+        </is>
+      </c>
+      <c r="D65" t="n">
+        <v>33.35035</v>
+      </c>
+      <c r="E65" t="n">
+        <v>130.943571</v>
+      </c>
+      <c r="F65" t="inlineStr">
+        <is>
+          <t>5分</t>
+        </is>
+      </c>
+      <c r="G65" t="inlineStr">
+        <is>
+          <t>【種別：指定避難所】【対応災害：洪水, 地震】【所在地：大分県日田市清水町1187】【連絡先：(0973)22-2284】</t>
+        </is>
+      </c>
+      <c r="H65" t="n">
+        <v>0</v>
+      </c>
+      <c r="I65" t="inlineStr">
+        <is>
+          <t>待機中</t>
+        </is>
+      </c>
+      <c r="J65" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="n">
+        <v>65</v>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>三花公民館</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>指定避難所</t>
+        </is>
+      </c>
+      <c r="D66" t="n">
+        <v>33.349709</v>
+      </c>
+      <c r="E66" t="n">
+        <v>130.942583</v>
+      </c>
+      <c r="F66" t="inlineStr">
+        <is>
+          <t>5分</t>
+        </is>
+      </c>
+      <c r="G66" t="inlineStr">
+        <is>
+          <t>【種別：指定避難所】【対応災害：洪水, 崖崩れ・土石流, 地震】【所在地：大分県日田市清水町948-1】【連絡先：(0973)24-3388】</t>
+        </is>
+      </c>
+      <c r="H66" t="n">
+        <v>0</v>
+      </c>
+      <c r="I66" t="inlineStr">
+        <is>
+          <t>待機中</t>
+        </is>
+      </c>
+      <c r="J66" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="n">
+        <v>66</v>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>北部中学校</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>指定避難所</t>
+        </is>
+      </c>
+      <c r="D67" t="n">
+        <v>33.336302</v>
+      </c>
+      <c r="E67" t="n">
+        <v>130.946513</v>
+      </c>
+      <c r="F67" t="inlineStr">
+        <is>
+          <t>5分</t>
+        </is>
+      </c>
+      <c r="G67" t="inlineStr">
+        <is>
+          <t>【種別：指定避難所】【対応災害：崖崩れ・土石流, 地震】【所在地：大分県日田市上手町148-1】【連絡先：(0973)23-6272】</t>
+        </is>
+      </c>
+      <c r="H67" t="n">
+        <v>0</v>
+      </c>
+      <c r="I67" t="inlineStr">
+        <is>
+          <t>待機中</t>
+        </is>
+      </c>
+      <c r="J67" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="n">
+        <v>67</v>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>花月コミュニティセンター</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>指定避難所</t>
+        </is>
+      </c>
+      <c r="D68" t="n">
+        <v>33.365716</v>
+      </c>
+      <c r="E68" t="n">
+        <v>130.971845</v>
+      </c>
+      <c r="F68" t="inlineStr">
+        <is>
+          <t>5分</t>
+        </is>
+      </c>
+      <c r="G68" t="inlineStr">
+        <is>
+          <t>【種別：指定避難所】【対応災害：洪水, 崖崩れ・土石流, 地震】【所在地：大分県日田市大字花月1436-1】【連絡先：(0973)24-9403】</t>
+        </is>
+      </c>
+      <c r="H68" t="n">
+        <v>0</v>
+      </c>
+      <c r="I68" t="inlineStr">
+        <is>
+          <t>待機中</t>
+        </is>
+      </c>
+      <c r="J68" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="n">
+        <v>68</v>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>伏木多目的交流館</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>指定避難所</t>
+        </is>
+      </c>
+      <c r="D69" t="n">
+        <v>33.381739</v>
+      </c>
+      <c r="E69" t="n">
+        <v>130.994074</v>
+      </c>
+      <c r="F69" t="inlineStr">
+        <is>
+          <t>5分</t>
+        </is>
+      </c>
+      <c r="G69" t="inlineStr">
+        <is>
+          <t>【種別：指定避難所】【対応災害：洪水, 崖崩れ・土石流】【所在地：大分県日田市伏木町3512】【連絡先：(0973)24-9606】</t>
+        </is>
+      </c>
+      <c r="H69" t="n">
+        <v>0</v>
+      </c>
+      <c r="I69" t="inlineStr">
+        <is>
+          <t>待機中</t>
+        </is>
+      </c>
+      <c r="J69" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="n">
+        <v>69</v>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>戸山中学校</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>指定避難所</t>
+        </is>
+      </c>
+      <c r="D70" t="n">
+        <v>33.361122</v>
+      </c>
+      <c r="E70" t="n">
+        <v>130.957877</v>
+      </c>
+      <c r="F70" t="inlineStr">
+        <is>
+          <t>5分</t>
+        </is>
+      </c>
+      <c r="G70" t="inlineStr">
+        <is>
+          <t>【種別：指定避難所】【対応災害：洪水, 地震】【所在地：大分県日田市藤山町213-1】【連絡先：(0973)24-9140】</t>
+        </is>
+      </c>
+      <c r="H70" t="n">
+        <v>0</v>
+      </c>
+      <c r="I70" t="inlineStr">
+        <is>
+          <t>待機中</t>
+        </is>
+      </c>
+      <c r="J70" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="n">
+        <v>70</v>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>小野小学校</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>指定避難所</t>
+        </is>
+      </c>
+      <c r="D71" t="n">
+        <v>33.393812</v>
+      </c>
+      <c r="E71" t="n">
+        <v>130.941501</v>
+      </c>
+      <c r="F71" t="inlineStr">
+        <is>
+          <t>5分</t>
+        </is>
+      </c>
+      <c r="G71" t="inlineStr">
+        <is>
+          <t>【種別：指定避難所】【対応災害：洪水, 地震】【所在地：大分県日田市鈴連町1658-1】【連絡先：(0973)29-2111】</t>
+        </is>
+      </c>
+      <c r="H71" t="n">
+        <v>0</v>
+      </c>
+      <c r="I71" t="inlineStr">
+        <is>
+          <t>待機中</t>
+        </is>
+      </c>
+      <c r="J71" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="n">
+        <v>71</v>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>小野公民館（振興センター）</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>指定避難所</t>
+        </is>
+      </c>
+      <c r="D72" t="n">
+        <v>33.381169</v>
+      </c>
+      <c r="E72" t="n">
+        <v>130.939897</v>
+      </c>
+      <c r="F72" t="inlineStr">
+        <is>
+          <t>5分</t>
+        </is>
+      </c>
+      <c r="G72" t="inlineStr">
+        <is>
+          <t>【種別：指定避難所】【対応災害：洪水, 崖崩れ・土石流, 地震】【所在地：大分県日田市鈴連町900-3】【連絡先：(0973)29-2201】</t>
+        </is>
+      </c>
+      <c r="H72" t="n">
+        <v>0</v>
+      </c>
+      <c r="I72" t="inlineStr">
+        <is>
+          <t>待機中</t>
+        </is>
+      </c>
+      <c r="J72" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="n">
+        <v>72</v>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>西有田公民館</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>指定避難所</t>
+        </is>
+      </c>
+      <c r="D73" t="n">
+        <v>33.33657</v>
+      </c>
+      <c r="E73" t="n">
+        <v>130.962165</v>
+      </c>
+      <c r="F73" t="inlineStr">
+        <is>
+          <t>5分</t>
+        </is>
+      </c>
+      <c r="G73" t="inlineStr">
+        <is>
+          <t>【種別：指定避難所】【対応災害：洪水, 崖崩れ・土石流, 地震】【所在地：大分県日田市石松町2927-1】【連絡先：(0973)22-4702】</t>
+        </is>
+      </c>
+      <c r="H73" t="n">
+        <v>0</v>
+      </c>
+      <c r="I73" t="inlineStr">
+        <is>
+          <t>待機中</t>
+        </is>
+      </c>
+      <c r="J73" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="n">
+        <v>73</v>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>大分県立日田支援学校</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>指定避難所</t>
+        </is>
+      </c>
+      <c r="D74" t="n">
+        <v>33.336786</v>
+      </c>
+      <c r="E74" t="n">
+        <v>130.961069</v>
+      </c>
+      <c r="F74" t="inlineStr">
+        <is>
+          <t>5分</t>
+        </is>
+      </c>
+      <c r="G74" t="inlineStr">
+        <is>
+          <t>【種別：指定避難所】【対応災害：洪水, 崖崩れ・土石流, 地震】【所在地：大分県日田市石松町2941-1】【連絡先：(0973)24-2000】</t>
+        </is>
+      </c>
+      <c r="H74" t="n">
+        <v>0</v>
+      </c>
+      <c r="I74" t="inlineStr">
+        <is>
+          <t>待機中</t>
+        </is>
+      </c>
+      <c r="J74" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="n">
+        <v>74</v>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>有田小学校</t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>指定避難所</t>
+        </is>
+      </c>
+      <c r="D75" t="n">
+        <v>33.330719</v>
+      </c>
+      <c r="E75" t="n">
+        <v>130.968344</v>
+      </c>
+      <c r="F75" t="inlineStr">
+        <is>
+          <t>5分</t>
+        </is>
+      </c>
+      <c r="G75" t="inlineStr">
+        <is>
+          <t>【種別：指定避難所】【対応災害：崖崩れ・土石流, 地震】【所在地：大分県日田市諸留町2687-1】【連絡先：(0973)24-2175】</t>
+        </is>
+      </c>
+      <c r="H75" t="n">
+        <v>0</v>
+      </c>
+      <c r="I75" t="inlineStr">
+        <is>
+          <t>待機中</t>
+        </is>
+      </c>
+      <c r="J75" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="n">
+        <v>75</v>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>東有田中学校</t>
+        </is>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>指定避難所</t>
+        </is>
+      </c>
+      <c r="D76" t="n">
+        <v>33.33093</v>
+      </c>
+      <c r="E76" t="n">
+        <v>130.98321</v>
+      </c>
+      <c r="F76" t="inlineStr">
+        <is>
+          <t>5分</t>
+        </is>
+      </c>
+      <c r="G76" t="inlineStr">
+        <is>
+          <t>【種別：指定避難所】【対応災害：地震】【所在地：大分県日田市諸留町488-2】【連絡先：(0973)24-8179】</t>
+        </is>
+      </c>
+      <c r="H76" t="n">
+        <v>0</v>
+      </c>
+      <c r="I76" t="inlineStr">
+        <is>
+          <t>待機中</t>
+        </is>
+      </c>
+      <c r="J76" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="n">
+        <v>76</v>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>東有田公民館</t>
+        </is>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>指定避難所</t>
+        </is>
+      </c>
+      <c r="D77" t="n">
+        <v>33.330785</v>
+      </c>
+      <c r="E77" t="n">
+        <v>130.979204</v>
+      </c>
+      <c r="F77" t="inlineStr">
+        <is>
+          <t>5分</t>
+        </is>
+      </c>
+      <c r="G77" t="inlineStr">
+        <is>
+          <t>【種別：指定避難所】【対応災害：崖崩れ・土石流】【所在地：大分県日田市諸留町52】【連絡先：(0973)24-8111】</t>
+        </is>
+      </c>
+      <c r="H77" t="n">
+        <v>0</v>
+      </c>
+      <c r="I77" t="inlineStr">
+        <is>
+          <t>待機中</t>
+        </is>
+      </c>
+      <c r="J77" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="n">
+        <v>77</v>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>羽田多目的交流館</t>
+        </is>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>指定避難所</t>
+        </is>
+      </c>
+      <c r="D78" t="n">
+        <v>33.334706</v>
+      </c>
+      <c r="E78" t="n">
+        <v>131.027672</v>
+      </c>
+      <c r="F78" t="inlineStr">
+        <is>
+          <t>5分</t>
+        </is>
+      </c>
+      <c r="G78" t="inlineStr">
+        <is>
+          <t>【種別：指定避難所】【対応災害：洪水, 崖崩れ・土石流, 地震】【所在地：大分県日田市日の本町2463-1】【連絡先：(0973)24-8421】</t>
+        </is>
+      </c>
+      <c r="H78" t="n">
+        <v>0</v>
+      </c>
+      <c r="I78" t="inlineStr">
+        <is>
+          <t>待機中</t>
+        </is>
+      </c>
+      <c r="J78" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="n">
+        <v>78</v>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>月出山多目的交流館</t>
+        </is>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>指定避難所</t>
+        </is>
+      </c>
+      <c r="D79" t="n">
+        <v>33.309882</v>
+      </c>
+      <c r="E79" t="n">
+        <v>131.025307</v>
+      </c>
+      <c r="F79" t="inlineStr">
+        <is>
+          <t>5分</t>
+        </is>
+      </c>
+      <c r="G79" t="inlineStr">
+        <is>
+          <t>【種別：指定避難所】【対応災害：洪水, 崖崩れ・土石流, 地震】【所在地：大分県日田市月出町5590】【連絡先：(0973)24-8767】</t>
+        </is>
+      </c>
+      <c r="H79" t="n">
+        <v>0</v>
+      </c>
+      <c r="I79" t="inlineStr">
+        <is>
+          <t>待機中</t>
+        </is>
+      </c>
+      <c r="J79" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="n">
+        <v>79</v>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>大明小中学校</t>
+        </is>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>指定避難所</t>
+        </is>
+      </c>
+      <c r="D80" t="n">
+        <v>33.364717</v>
+      </c>
+      <c r="E80" t="n">
+        <v>130.882685</v>
+      </c>
+      <c r="F80" t="inlineStr">
+        <is>
+          <t>5分</t>
+        </is>
+      </c>
+      <c r="G80" t="inlineStr">
+        <is>
+          <t>【種別：指定避難所】【対応災害：洪水, 地震】【所在地：大分県日田市大肥本町1701】【連絡先：(0973)28-2224】</t>
+        </is>
+      </c>
+      <c r="H80" t="n">
+        <v>0</v>
+      </c>
+      <c r="I80" t="inlineStr">
+        <is>
+          <t>待機中</t>
+        </is>
+      </c>
+      <c r="J80" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="n">
+        <v>80</v>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>大鶴公民館</t>
+        </is>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>指定避難所</t>
+        </is>
+      </c>
+      <c r="D81" t="n">
+        <v>33.370873</v>
+      </c>
+      <c r="E81" t="n">
+        <v>130.889835</v>
+      </c>
+      <c r="F81" t="inlineStr">
+        <is>
+          <t>5分</t>
+        </is>
+      </c>
+      <c r="G81" t="inlineStr">
+        <is>
+          <t>【種別：指定避難所】【対応災害：洪水, 崖崩れ・土石流, 地震】【所在地：大分県日田市大鶴本町870】【連絡先：(0973)28-2121】</t>
+        </is>
+      </c>
+      <c r="H81" t="n">
+        <v>0</v>
+      </c>
+      <c r="I81" t="inlineStr">
+        <is>
+          <t>待機中</t>
+        </is>
+      </c>
+      <c r="J81" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="n">
+        <v>81</v>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>夜明公民館</t>
+        </is>
+      </c>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>指定避難所</t>
+        </is>
+      </c>
+      <c r="D82" t="n">
+        <v>33.325002</v>
+      </c>
+      <c r="E82" t="n">
+        <v>130.87073</v>
+      </c>
+      <c r="F82" t="inlineStr">
+        <is>
+          <t>5分</t>
+        </is>
+      </c>
+      <c r="G82" t="inlineStr">
+        <is>
+          <t>【種別：指定避難所】【対応災害：洪水, 崖崩れ・土石流, 地震】【所在地：大分県日田市夜明中町1547】【連絡先：(0973)27-2121】</t>
+        </is>
+      </c>
+      <c r="H82" t="n">
+        <v>0</v>
+      </c>
+      <c r="I82" t="inlineStr">
+        <is>
+          <t>待機中</t>
+        </is>
+      </c>
+      <c r="J82" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="n">
+        <v>82</v>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>石井小学校</t>
+        </is>
+      </c>
+      <c r="C83" t="inlineStr">
+        <is>
+          <t>指定避難所</t>
+        </is>
+      </c>
+      <c r="D83" t="n">
+        <v>33.310797</v>
+      </c>
+      <c r="E83" t="n">
+        <v>130.908156</v>
+      </c>
+      <c r="F83" t="inlineStr">
+        <is>
+          <t>5分</t>
+        </is>
+      </c>
+      <c r="G83" t="inlineStr">
+        <is>
+          <t>【種別：指定避難所】【対応災害：崖崩れ・土石流, 地震】【所在地：大分県日田市石井町二丁目478】【連絡先：(0973)22-3442】</t>
+        </is>
+      </c>
+      <c r="H83" t="n">
+        <v>0</v>
+      </c>
+      <c r="I83" t="inlineStr">
+        <is>
+          <t>待機中</t>
+        </is>
+      </c>
+      <c r="J83" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="n">
+        <v>83</v>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>五和公民館</t>
+        </is>
+      </c>
+      <c r="C84" t="inlineStr">
+        <is>
+          <t>指定避難所</t>
+        </is>
+      </c>
+      <c r="D84" t="n">
+        <v>33.312333</v>
+      </c>
+      <c r="E84" t="n">
+        <v>130.911463</v>
+      </c>
+      <c r="F84" t="inlineStr">
+        <is>
+          <t>5分</t>
+        </is>
+      </c>
+      <c r="G84" t="inlineStr">
+        <is>
+          <t>【種別：指定避難所】【対応災害：洪水, 崖崩れ・土石流, 地震】【所在地：大分県日田市石井町一丁目274-4】【連絡先：(0973)22-4126】</t>
+        </is>
+      </c>
+      <c r="H84" t="n">
+        <v>0</v>
+      </c>
+      <c r="I84" t="inlineStr">
+        <is>
+          <t>待機中</t>
+        </is>
+      </c>
+      <c r="J84" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="n">
+        <v>84</v>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>柚木多目的交流館</t>
+        </is>
+      </c>
+      <c r="C85" t="inlineStr">
+        <is>
+          <t>指定避難所</t>
+        </is>
+      </c>
+      <c r="D85" t="n">
+        <v>33.255531</v>
+      </c>
+      <c r="E85" t="n">
+        <v>130.848763</v>
+      </c>
+      <c r="F85" t="inlineStr">
+        <is>
+          <t>5分</t>
+        </is>
+      </c>
+      <c r="G85" t="inlineStr">
+        <is>
+          <t>【種別：指定避難所】【対応災害：洪水, 地震】【所在地：大分県日田市前津江町柚木451】</t>
+        </is>
+      </c>
+      <c r="H85" t="n">
+        <v>0</v>
+      </c>
+      <c r="I85" t="inlineStr">
+        <is>
+          <t>待機中</t>
+        </is>
+      </c>
+      <c r="J85" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="n">
+        <v>85</v>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>旧出野小学校</t>
+        </is>
+      </c>
+      <c r="C86" t="inlineStr">
+        <is>
+          <t>指定避難所</t>
+        </is>
+      </c>
+      <c r="D86" t="n">
+        <v>33.21997</v>
+      </c>
+      <c r="E86" t="n">
+        <v>130.883701</v>
+      </c>
+      <c r="F86" t="inlineStr">
+        <is>
+          <t>5分</t>
+        </is>
+      </c>
+      <c r="G86" t="inlineStr">
+        <is>
+          <t>【種別：指定避難所】【対応災害：洪水, 崖崩れ・土石流, 地震】【所在地：大分県日田市前津江町柚木2194-1】</t>
+        </is>
+      </c>
+      <c r="H86" t="n">
+        <v>0</v>
+      </c>
+      <c r="I86" t="inlineStr">
+        <is>
+          <t>待機中</t>
+        </is>
+      </c>
+      <c r="J86" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="n">
+        <v>86</v>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>前津江小学校</t>
+        </is>
+      </c>
+      <c r="C87" t="inlineStr">
+        <is>
+          <t>指定避難所</t>
+        </is>
+      </c>
+      <c r="D87" t="n">
+        <v>33.210507</v>
+      </c>
+      <c r="E87" t="n">
+        <v>130.92048</v>
+      </c>
+      <c r="F87" t="inlineStr">
+        <is>
+          <t>5分</t>
+        </is>
+      </c>
+      <c r="G87" t="inlineStr">
+        <is>
+          <t>【種別：指定避難所】【対応災害：洪水, 地震】【所在地：大分県日田市前津江町大野2562】【連絡先：(0973)53-2210】</t>
+        </is>
+      </c>
+      <c r="H87" t="n">
+        <v>0</v>
+      </c>
+      <c r="I87" t="inlineStr">
+        <is>
+          <t>待機中</t>
+        </is>
+      </c>
+      <c r="J87" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="n">
+        <v>87</v>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>曽家多目的交流館</t>
+        </is>
+      </c>
+      <c r="C88" t="inlineStr">
+        <is>
+          <t>指定避難所</t>
+        </is>
+      </c>
+      <c r="D88" t="n">
+        <v>33.192879</v>
+      </c>
+      <c r="E88" t="n">
+        <v>130.968023</v>
+      </c>
+      <c r="F88" t="inlineStr">
+        <is>
+          <t>5分</t>
+        </is>
+      </c>
+      <c r="G88" t="inlineStr">
+        <is>
+          <t>【種別：指定避難所】【対応災害：洪水, 地震】【所在地：大分県日田市前津江町赤石3121-2】</t>
+        </is>
+      </c>
+      <c r="H88" t="n">
+        <v>0</v>
+      </c>
+      <c r="I88" t="inlineStr">
+        <is>
+          <t>待機中</t>
+        </is>
+      </c>
+      <c r="J88" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="n">
+        <v>88</v>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>前津江中学校</t>
+        </is>
+      </c>
+      <c r="C89" t="inlineStr">
+        <is>
+          <t>指定避難所</t>
+        </is>
+      </c>
+      <c r="D89" t="n">
+        <v>33.211343</v>
+      </c>
+      <c r="E89" t="n">
+        <v>130.916692</v>
+      </c>
+      <c r="F89" t="inlineStr">
+        <is>
+          <t>5分</t>
+        </is>
+      </c>
+      <c r="G89" t="inlineStr">
+        <is>
+          <t>【種別：指定避難所】【対応災害：洪水, 地震】【所在地：大分県日田市前津江町大野2214】【連絡先：(0973)53-2211】</t>
+        </is>
+      </c>
+      <c r="H89" t="n">
+        <v>0</v>
+      </c>
+      <c r="I89" t="inlineStr">
+        <is>
+          <t>待機中</t>
+        </is>
+      </c>
+      <c r="J89" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="n">
+        <v>89</v>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>出野地区交流センター</t>
+        </is>
+      </c>
+      <c r="C90" t="inlineStr">
+        <is>
+          <t>指定避難所</t>
+        </is>
+      </c>
+      <c r="D90" t="n">
+        <v>33.219441</v>
+      </c>
+      <c r="E90" t="n">
+        <v>130.884156</v>
+      </c>
+      <c r="F90" t="inlineStr">
+        <is>
+          <t>5分</t>
+        </is>
+      </c>
+      <c r="G90" t="inlineStr">
+        <is>
+          <t>【種別：指定避難所】【対応災害：洪水, 崖崩れ・土石流, 地震】【所在地：大分県日田市前津江町柚木2185-1】【連絡先：(0973)53-2162】</t>
+        </is>
+      </c>
+      <c r="H90" t="n">
+        <v>0</v>
+      </c>
+      <c r="I90" t="inlineStr">
+        <is>
+          <t>待機中</t>
+        </is>
+      </c>
+      <c r="J90" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="n">
+        <v>90</v>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>前津江町地域活性化センター</t>
+        </is>
+      </c>
+      <c r="C91" t="inlineStr">
+        <is>
+          <t>指定避難所</t>
+        </is>
+      </c>
+      <c r="D91" t="n">
+        <v>33.191644</v>
+      </c>
+      <c r="E91" t="n">
+        <v>130.915598</v>
+      </c>
+      <c r="F91" t="inlineStr">
+        <is>
+          <t>5分</t>
+        </is>
+      </c>
+      <c r="G91" t="inlineStr">
+        <is>
+          <t>【種別：指定避難所】【対応災害：洪水, 崖崩れ・土石流, 地震】【所在地：大分県日田市前津江町大野70-15】【連絡先：(0973)53-2041】</t>
+        </is>
+      </c>
+      <c r="H91" t="n">
+        <v>0</v>
+      </c>
+      <c r="I91" t="inlineStr">
+        <is>
+          <t>待機中</t>
+        </is>
+      </c>
+      <c r="J91" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="n">
+        <v>91</v>
+      </c>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>まえつえ保育園</t>
+        </is>
+      </c>
+      <c r="C92" t="inlineStr">
+        <is>
+          <t>指定避難所</t>
+        </is>
+      </c>
+      <c r="D92" t="n">
+        <v>33.210234</v>
+      </c>
+      <c r="E92" t="n">
+        <v>130.917991</v>
+      </c>
+      <c r="F92" t="inlineStr">
+        <is>
+          <t>5分</t>
+        </is>
+      </c>
+      <c r="G92" t="inlineStr">
+        <is>
+          <t>【種別：指定避難所】【対応災害：洪水, 地震】【所在地：大分県日田市前津江町大野2188】【連絡先：(0973)53-2409】</t>
+        </is>
+      </c>
+      <c r="H92" t="n">
+        <v>0</v>
+      </c>
+      <c r="I92" t="inlineStr">
+        <is>
+          <t>待機中</t>
+        </is>
+      </c>
+      <c r="J92" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="n">
+        <v>92</v>
+      </c>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>前津江町柔剣道場</t>
+        </is>
+      </c>
+      <c r="C93" t="inlineStr">
+        <is>
+          <t>指定避難所</t>
+        </is>
+      </c>
+      <c r="D93" t="n">
+        <v>33.209487</v>
+      </c>
+      <c r="E93" t="n">
+        <v>130.918807</v>
+      </c>
+      <c r="F93" t="inlineStr">
+        <is>
+          <t>5分</t>
+        </is>
+      </c>
+      <c r="G93" t="inlineStr">
+        <is>
+          <t>【種別：指定避難所】【対応災害：洪水, 地震】【所在地：大分県日田市前津江町大野2179-2】【連絡先：(0973)53-2111】</t>
+        </is>
+      </c>
+      <c r="H93" t="n">
+        <v>0</v>
+      </c>
+      <c r="I93" t="inlineStr">
+        <is>
+          <t>待機中</t>
+        </is>
+      </c>
+      <c r="J93" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="n">
+        <v>93</v>
+      </c>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>赤石老人憩の家</t>
+        </is>
+      </c>
+      <c r="C94" t="inlineStr">
+        <is>
+          <t>指定避難所</t>
+        </is>
+      </c>
+      <c r="D94" t="n">
+        <v>33.202653</v>
+      </c>
+      <c r="E94" t="n">
+        <v>130.937627</v>
+      </c>
+      <c r="F94" t="inlineStr">
+        <is>
+          <t>5分</t>
+        </is>
+      </c>
+      <c r="G94" t="inlineStr">
+        <is>
+          <t>【種別：指定避難所】【対応災害：洪水】【所在地：大分県日田市前津江町赤石1932-1】</t>
+        </is>
+      </c>
+      <c r="H94" t="n">
+        <v>0</v>
+      </c>
+      <c r="I94" t="inlineStr">
+        <is>
+          <t>待機中</t>
+        </is>
+      </c>
+      <c r="J94" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="n">
+        <v>94</v>
+      </c>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>中津江振興局</t>
+        </is>
+      </c>
+      <c r="C95" t="inlineStr">
+        <is>
+          <t>指定避難所</t>
+        </is>
+      </c>
+      <c r="D95" t="n">
+        <v>33.128978</v>
+      </c>
+      <c r="E95" t="n">
+        <v>130.951408</v>
+      </c>
+      <c r="F95" t="inlineStr">
+        <is>
+          <t>5分</t>
+        </is>
+      </c>
+      <c r="G95" t="inlineStr">
+        <is>
+          <t>【種別：指定避難所】【対応災害：洪水, 地震】【所在地：大分県日田市中津江村栃野2357-1】【連絡先：(0973)54-3111】</t>
+        </is>
+      </c>
+      <c r="H95" t="n">
+        <v>0</v>
+      </c>
+      <c r="I95" t="inlineStr">
+        <is>
+          <t>待機中</t>
+        </is>
+      </c>
+      <c r="J95" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="n">
+        <v>95</v>
+      </c>
+      <c r="B96" t="inlineStr">
+        <is>
+          <t>津江小中学校</t>
+        </is>
+      </c>
+      <c r="C96" t="inlineStr">
+        <is>
+          <t>指定避難所</t>
+        </is>
+      </c>
+      <c r="D96" t="n">
+        <v>33.140049</v>
+      </c>
+      <c r="E96" t="n">
+        <v>130.971424</v>
+      </c>
+      <c r="F96" t="inlineStr">
+        <is>
+          <t>5分</t>
+        </is>
+      </c>
+      <c r="G96" t="inlineStr">
+        <is>
+          <t>【種別：指定避難所】【対応災害：洪水, 崖崩れ・土石流, 地震】【所在地：大分県日田市中津江村栃野4341】【連絡先：(0973)54-3116】</t>
+        </is>
+      </c>
+      <c r="H96" t="n">
+        <v>0</v>
+      </c>
+      <c r="I96" t="inlineStr">
+        <is>
+          <t>待機中</t>
+        </is>
+      </c>
+      <c r="J96" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="n">
+        <v>96</v>
+      </c>
+      <c r="B97" t="inlineStr">
+        <is>
+          <t>Ｂ＆Ｇ中津江海洋センター</t>
+        </is>
+      </c>
+      <c r="C97" t="inlineStr">
+        <is>
+          <t>指定避難所</t>
+        </is>
+      </c>
+      <c r="D97" t="n">
+        <v>33.136302</v>
+      </c>
+      <c r="E97" t="n">
+        <v>130.90672</v>
+      </c>
+      <c r="F97" t="inlineStr">
+        <is>
+          <t>5分</t>
+        </is>
+      </c>
+      <c r="G97" t="inlineStr">
+        <is>
+          <t>【種別：指定避難所】【対応災害：洪水, 崖崩れ・土石流, 地震】【所在地：大分県日田市中津江村合瀬1936-28】【連絡先：(0973)56-5016】</t>
+        </is>
+      </c>
+      <c r="H97" t="n">
+        <v>0</v>
+      </c>
+      <c r="I97" t="inlineStr">
+        <is>
+          <t>待機中</t>
+        </is>
+      </c>
+      <c r="J97" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="n">
+        <v>97</v>
+      </c>
+      <c r="B98" t="inlineStr">
+        <is>
+          <t>地底博物館鯛生金山</t>
+        </is>
+      </c>
+      <c r="C98" t="inlineStr">
+        <is>
+          <t>指定避難所</t>
+        </is>
+      </c>
+      <c r="D98" t="n">
+        <v>33.128346</v>
+      </c>
+      <c r="E98" t="n">
+        <v>130.882143</v>
+      </c>
+      <c r="F98" t="inlineStr">
+        <is>
+          <t>5分</t>
+        </is>
+      </c>
+      <c r="G98" t="inlineStr">
+        <is>
+          <t>【種別：指定避難所】【対応災害：洪水】【所在地：大分県日田市中津江村合瀬3750】【連絡先：(0973)56-5316】</t>
+        </is>
+      </c>
+      <c r="H98" t="n">
+        <v>0</v>
+      </c>
+      <c r="I98" t="inlineStr">
+        <is>
+          <t>待機中</t>
+        </is>
+      </c>
+      <c r="J98" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="n">
+        <v>98</v>
+      </c>
+      <c r="B99" t="inlineStr">
+        <is>
+          <t>上津江体育館</t>
+        </is>
+      </c>
+      <c r="C99" t="inlineStr">
+        <is>
+          <t>指定避難所</t>
+        </is>
+      </c>
+      <c r="D99" t="n">
+        <v>33.094863</v>
+      </c>
+      <c r="E99" t="n">
+        <v>130.976624</v>
+      </c>
+      <c r="F99" t="inlineStr">
+        <is>
+          <t>5分</t>
+        </is>
+      </c>
+      <c r="G99" t="inlineStr">
+        <is>
+          <t>【種別：指定避難所】【対応災害：洪水, 崖崩れ・土石流, 地震】【所在地：大分県日田市上津江町川原2710】【連絡先：(0973)55-2011】</t>
+        </is>
+      </c>
+      <c r="H99" t="n">
+        <v>0</v>
+      </c>
+      <c r="I99" t="inlineStr">
+        <is>
+          <t>待機中</t>
+        </is>
+      </c>
+      <c r="J99" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="n">
+        <v>99</v>
+      </c>
+      <c r="B100" t="inlineStr">
+        <is>
+          <t>上津江第5分団消防詰所</t>
+        </is>
+      </c>
+      <c r="C100" t="inlineStr">
+        <is>
+          <t>指定避難所</t>
+        </is>
+      </c>
+      <c r="D100" t="n">
+        <v>33.054331</v>
+      </c>
+      <c r="E100" t="n">
+        <v>130.98715</v>
+      </c>
+      <c r="F100" t="inlineStr">
+        <is>
+          <t>5分</t>
+        </is>
+      </c>
+      <c r="G100" t="inlineStr">
+        <is>
+          <t>【種別：指定避難所】【対応災害：洪水, 地震】【所在地：大分県日田市上津江町上野田1217-9】</t>
+        </is>
+      </c>
+      <c r="H100" t="n">
+        <v>0</v>
+      </c>
+      <c r="I100" t="inlineStr">
+        <is>
+          <t>待機中</t>
+        </is>
+      </c>
+      <c r="J100" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="n">
+        <v>100</v>
+      </c>
+      <c r="B101" t="inlineStr">
+        <is>
+          <t>川原自治会センター</t>
+        </is>
+      </c>
+      <c r="C101" t="inlineStr">
+        <is>
+          <t>指定避難所</t>
+        </is>
+      </c>
+      <c r="D101" t="n">
+        <v>33.112812</v>
+      </c>
+      <c r="E101" t="n">
+        <v>130.962029</v>
+      </c>
+      <c r="F101" t="inlineStr">
+        <is>
+          <t>5分</t>
+        </is>
+      </c>
+      <c r="G101" t="inlineStr">
+        <is>
+          <t>【種別：指定避難所】【対応災害：洪水】【所在地：大分県日田市上津江町川原3852-1】</t>
+        </is>
+      </c>
+      <c r="H101" t="n">
+        <v>0</v>
+      </c>
+      <c r="I101" t="inlineStr">
+        <is>
+          <t>待機中</t>
+        </is>
+      </c>
+      <c r="J101" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="n">
+        <v>101</v>
+      </c>
+      <c r="B102" t="inlineStr">
+        <is>
+          <t>旧鎌手小学校</t>
+        </is>
+      </c>
+      <c r="C102" t="inlineStr">
+        <is>
+          <t>指定避難所</t>
+        </is>
+      </c>
+      <c r="D102" t="n">
+        <v>33.232099</v>
+      </c>
+      <c r="E102" t="n">
+        <v>130.979118</v>
+      </c>
+      <c r="F102" t="inlineStr">
+        <is>
+          <t>5分</t>
+        </is>
+      </c>
+      <c r="G102" t="inlineStr">
+        <is>
+          <t>【種別：指定避難所】【対応災害：洪水, 崖崩れ・土石流, 地震】【所在地：大分県日田市大山町西大山5926-3】</t>
+        </is>
+      </c>
+      <c r="H102" t="n">
+        <v>0</v>
+      </c>
+      <c r="I102" t="inlineStr">
+        <is>
+          <t>待機中</t>
+        </is>
+      </c>
+      <c r="J102" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="n">
+        <v>102</v>
+      </c>
+      <c r="B103" t="inlineStr">
+        <is>
+          <t>旧都築小学校</t>
+        </is>
+      </c>
+      <c r="C103" t="inlineStr">
+        <is>
+          <t>指定避難所</t>
+        </is>
+      </c>
+      <c r="D103" t="n">
+        <v>33.262038</v>
+      </c>
+      <c r="E103" t="n">
+        <v>130.988807</v>
+      </c>
+      <c r="F103" t="inlineStr">
+        <is>
+          <t>5分</t>
+        </is>
+      </c>
+      <c r="G103" t="inlineStr">
+        <is>
+          <t>【種別：指定避難所】【対応災害：洪水, 崖崩れ・土石流, 地震】【所在地：大分県日田市大山町東大山1125】【連絡先：(0973)52-3006】</t>
+        </is>
+      </c>
+      <c r="H103" t="n">
+        <v>0</v>
+      </c>
+      <c r="I103" t="inlineStr">
+        <is>
+          <t>待機中</t>
+        </is>
+      </c>
+      <c r="J103" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="n">
+        <v>103</v>
+      </c>
+      <c r="B104" t="inlineStr">
+        <is>
+          <t>旧大山中学校体育館</t>
+        </is>
+      </c>
+      <c r="C104" t="inlineStr">
+        <is>
+          <t>指定避難所</t>
+        </is>
+      </c>
+      <c r="D104" t="n">
+        <v>33.24409</v>
+      </c>
+      <c r="E104" t="n">
+        <v>130.975885</v>
+      </c>
+      <c r="F104" t="inlineStr">
+        <is>
+          <t>5分</t>
+        </is>
+      </c>
+      <c r="G104" t="inlineStr">
+        <is>
+          <t>【種別：指定避難所】【対応災害：洪水】【所在地：大分県日田市大山町西大山4267】</t>
+        </is>
+      </c>
+      <c r="H104" t="n">
+        <v>0</v>
+      </c>
+      <c r="I104" t="inlineStr">
+        <is>
+          <t>待機中</t>
+        </is>
+      </c>
+      <c r="J104" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="n">
+        <v>104</v>
+      </c>
+      <c r="B105" t="inlineStr">
+        <is>
+          <t>松原児童館</t>
+        </is>
+      </c>
+      <c r="C105" t="inlineStr">
+        <is>
+          <t>指定避難所</t>
+        </is>
+      </c>
+      <c r="D105" t="n">
+        <v>33.200333</v>
+      </c>
+      <c r="E105" t="n">
+        <v>130.98862</v>
+      </c>
+      <c r="F105" t="inlineStr">
+        <is>
+          <t>5分</t>
+        </is>
+      </c>
+      <c r="G105" t="inlineStr">
+        <is>
+          <t>【種別：指定避難所】【対応災害：洪水】【所在地：大分県日田市大山町西大山8442-3】【連絡先：(0973)52-2922】</t>
+        </is>
+      </c>
+      <c r="H105" t="n">
+        <v>0</v>
+      </c>
+      <c r="I105" t="inlineStr">
+        <is>
+          <t>待機中</t>
+        </is>
+      </c>
+      <c r="J105" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="n">
+        <v>105</v>
+      </c>
+      <c r="B106" t="inlineStr">
+        <is>
+          <t>南部コミュニティーセンター</t>
+        </is>
+      </c>
+      <c r="C106" t="inlineStr">
+        <is>
+          <t>指定避難所</t>
+        </is>
+      </c>
+      <c r="D106" t="n">
+        <v>33.193489</v>
+      </c>
+      <c r="E106" t="n">
+        <v>130.988706</v>
+      </c>
+      <c r="F106" t="inlineStr">
+        <is>
+          <t>5分</t>
+        </is>
+      </c>
+      <c r="G106" t="inlineStr">
+        <is>
+          <t>【種別：指定避難所】【対応災害：洪水, 崖崩れ・土石流, 地震】【所在地：大分県日田市大山町西大山8504-1地先】</t>
+        </is>
+      </c>
+      <c r="H106" t="n">
+        <v>0</v>
+      </c>
+      <c r="I106" t="inlineStr">
+        <is>
+          <t>待機中</t>
+        </is>
+      </c>
+      <c r="J106" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="n">
+        <v>106</v>
+      </c>
+      <c r="B107" t="inlineStr">
+        <is>
+          <t>西峰コミュニティーセンター</t>
+        </is>
+      </c>
+      <c r="C107" t="inlineStr">
+        <is>
+          <t>指定避難所</t>
+        </is>
+      </c>
+      <c r="D107" t="n">
+        <v>33.249849</v>
+      </c>
+      <c r="E107" t="n">
+        <v>130.956418</v>
+      </c>
+      <c r="F107" t="inlineStr">
+        <is>
+          <t>5分</t>
+        </is>
+      </c>
+      <c r="G107" t="inlineStr">
+        <is>
+          <t>【種別：指定避難所】【対応災害：洪水】【所在地：大分県日田市大山町西大山2042-9】</t>
+        </is>
+      </c>
+      <c r="H107" t="n">
+        <v>0</v>
+      </c>
+      <c r="I107" t="inlineStr">
+        <is>
+          <t>待機中</t>
+        </is>
+      </c>
+      <c r="J107" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="n">
+        <v>107</v>
+      </c>
+      <c r="B108" t="inlineStr">
+        <is>
+          <t>老松コミュニティーセンター</t>
+        </is>
+      </c>
+      <c r="C108" t="inlineStr">
+        <is>
+          <t>指定避難所</t>
+        </is>
+      </c>
+      <c r="D108" t="n">
+        <v>33.260563</v>
+      </c>
+      <c r="E108" t="n">
+        <v>130.960748</v>
+      </c>
+      <c r="F108" t="inlineStr">
+        <is>
+          <t>5分</t>
+        </is>
+      </c>
+      <c r="G108" t="inlineStr">
+        <is>
+          <t>【種別：指定避難所】【対応災害：洪水, 崖崩れ・土石流, 地震】【所在地：大分県日田市大山町西大山870-5】</t>
+        </is>
+      </c>
+      <c r="H108" t="n">
+        <v>0</v>
+      </c>
+      <c r="I108" t="inlineStr">
+        <is>
+          <t>待機中</t>
+        </is>
+      </c>
+      <c r="J108" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="n">
+        <v>108</v>
+      </c>
+      <c r="B109" t="inlineStr">
+        <is>
+          <t>都築コミュニティーセンター</t>
+        </is>
+      </c>
+      <c r="C109" t="inlineStr">
+        <is>
+          <t>指定避難所</t>
+        </is>
+      </c>
+      <c r="D109" t="n">
+        <v>33.26147</v>
+      </c>
+      <c r="E109" t="n">
+        <v>130.988365</v>
+      </c>
+      <c r="F109" t="inlineStr">
+        <is>
+          <t>5分</t>
+        </is>
+      </c>
+      <c r="G109" t="inlineStr">
+        <is>
+          <t>【種別：指定避難所】【対応災害：洪水, 崖崩れ・土石流, 地震】【所在地：大分県日田市大山町東大山1157】</t>
+        </is>
+      </c>
+      <c r="H109" t="n">
+        <v>0</v>
+      </c>
+      <c r="I109" t="inlineStr">
+        <is>
+          <t>待機中</t>
+        </is>
+      </c>
+      <c r="J109" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="n">
+        <v>109</v>
+      </c>
+      <c r="B110" t="inlineStr">
+        <is>
+          <t>北部コミュニティーセンター</t>
+        </is>
+      </c>
+      <c r="C110" t="inlineStr">
+        <is>
+          <t>指定避難所</t>
+        </is>
+      </c>
+      <c r="D110" t="n">
+        <v>33.274529</v>
+      </c>
+      <c r="E110" t="n">
+        <v>130.955332</v>
+      </c>
+      <c r="F110" t="inlineStr">
+        <is>
+          <t>5分</t>
+        </is>
+      </c>
+      <c r="G110" t="inlineStr">
+        <is>
+          <t>【種別：指定避難所】【対応災害：洪水, 崖崩れ・土石流, 地震】【所在地：大分県日田市大山町東大山470-3】</t>
+        </is>
+      </c>
+      <c r="H110" t="n">
+        <v>0</v>
+      </c>
+      <c r="I110" t="inlineStr">
+        <is>
+          <t>待機中</t>
+        </is>
+      </c>
+      <c r="J110" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="n">
+        <v>110</v>
+      </c>
+      <c r="B111" t="inlineStr">
+        <is>
+          <t>大山文化センター（大山公民館）</t>
+        </is>
+      </c>
+      <c r="C111" t="inlineStr">
+        <is>
+          <t>指定避難所</t>
+        </is>
+      </c>
+      <c r="D111" t="n">
+        <v>33.257723</v>
+      </c>
+      <c r="E111" t="n">
+        <v>130.968088</v>
+      </c>
+      <c r="F111" t="inlineStr">
+        <is>
+          <t>5分</t>
+        </is>
+      </c>
+      <c r="G111" t="inlineStr">
+        <is>
+          <t>【種別：指定避難所】【対応災害：洪水】【所在地：大分県日田市大山町西大山3600】【連絡先：(0973)52-3101】</t>
+        </is>
+      </c>
+      <c r="H111" t="n">
+        <v>0</v>
+      </c>
+      <c r="I111" t="inlineStr">
+        <is>
+          <t>待機中</t>
+        </is>
+      </c>
+      <c r="J111" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" t="n">
+        <v>111</v>
+      </c>
+      <c r="B112" t="inlineStr">
+        <is>
+          <t>大山小中学校</t>
+        </is>
+      </c>
+      <c r="C112" t="inlineStr">
+        <is>
+          <t>指定避難所</t>
+        </is>
+      </c>
+      <c r="D112" t="n">
+        <v>33.257112</v>
+      </c>
+      <c r="E112" t="n">
+        <v>130.96924</v>
+      </c>
+      <c r="F112" t="inlineStr">
+        <is>
+          <t>5分</t>
+        </is>
+      </c>
+      <c r="G112" t="inlineStr">
+        <is>
+          <t>【種別：指定避難所】【対応災害：地震】【所在地：大分県日田市大山町西大山3615-1】【連絡先：(0973)52-2051】</t>
+        </is>
+      </c>
+      <c r="H112" t="n">
+        <v>0</v>
+      </c>
+      <c r="I112" t="inlineStr">
+        <is>
+          <t>待機中</t>
+        </is>
+      </c>
+      <c r="J112" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="n">
+        <v>112</v>
+      </c>
+      <c r="B113" t="inlineStr">
+        <is>
+          <t>旧台小学校</t>
+        </is>
+      </c>
+      <c r="C113" t="inlineStr">
+        <is>
+          <t>指定避難所</t>
+        </is>
+      </c>
+      <c r="D113" t="n">
+        <v>33.282529</v>
+      </c>
+      <c r="E113" t="n">
+        <v>130.97721</v>
+      </c>
+      <c r="F113" t="inlineStr">
+        <is>
+          <t>5分</t>
+        </is>
+      </c>
+      <c r="G113" t="inlineStr">
+        <is>
+          <t>【種別：指定避難所】【対応災害：洪水, 崖崩れ・土石流, 地震】【所在地：大分県日田市天瀬町女子畑1298-1】【連絡先：(0973)57-3031】</t>
+        </is>
+      </c>
+      <c r="H113" t="n">
+        <v>0</v>
+      </c>
+      <c r="I113" t="inlineStr">
+        <is>
+          <t>待機中</t>
+        </is>
+      </c>
+      <c r="J113" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" t="n">
+        <v>113</v>
+      </c>
+      <c r="B114" t="inlineStr">
+        <is>
+          <t>丸山コミュニティセンター</t>
+        </is>
+      </c>
+      <c r="C114" t="inlineStr">
+        <is>
+          <t>指定避難所</t>
+        </is>
+      </c>
+      <c r="D114" t="n">
+        <v>33.274032</v>
+      </c>
+      <c r="E114" t="n">
+        <v>131.000462</v>
+      </c>
+      <c r="F114" t="inlineStr">
+        <is>
+          <t>5分</t>
+        </is>
+      </c>
+      <c r="G114" t="inlineStr">
+        <is>
+          <t>【種別：指定避難所】【対応災害：洪水】【所在地：大分県日田市天瀬町合田747-1】【連絡先：(0973)57-2507】</t>
+        </is>
+      </c>
+      <c r="H114" t="n">
+        <v>0</v>
+      </c>
+      <c r="I114" t="inlineStr">
+        <is>
+          <t>待機中</t>
+        </is>
+      </c>
+      <c r="J114" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" t="n">
+        <v>114</v>
+      </c>
+      <c r="B115" t="inlineStr">
+        <is>
+          <t>旧桜竹小学校</t>
+        </is>
+      </c>
+      <c r="C115" t="inlineStr">
+        <is>
+          <t>指定避難所</t>
+        </is>
+      </c>
+      <c r="D115" t="n">
+        <v>33.250378</v>
+      </c>
+      <c r="E115" t="n">
+        <v>131.035284</v>
+      </c>
+      <c r="F115" t="inlineStr">
+        <is>
+          <t>5分</t>
+        </is>
+      </c>
+      <c r="G115" t="inlineStr">
+        <is>
+          <t>【種別：指定避難所】【対応災害：洪水, 崖崩れ・土石流, 地震】【所在地：大分県日田市天瀬町桜竹244-1】【連絡先：(0973)57-3030】</t>
+        </is>
+      </c>
+      <c r="H115" t="n">
+        <v>0</v>
+      </c>
+      <c r="I115" t="inlineStr">
+        <is>
+          <t>待機中</t>
+        </is>
+      </c>
+      <c r="J115" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" t="n">
+        <v>115</v>
+      </c>
+      <c r="B116" t="inlineStr">
+        <is>
+          <t>出口コミュニティセンター</t>
+        </is>
+      </c>
+      <c r="C116" t="inlineStr">
+        <is>
+          <t>指定避難所</t>
+        </is>
+      </c>
+      <c r="D116" t="n">
+        <v>33.204282</v>
+      </c>
+      <c r="E116" t="n">
+        <v>131.014288</v>
+      </c>
+      <c r="F116" t="inlineStr">
+        <is>
+          <t>5分</t>
+        </is>
+      </c>
+      <c r="G116" t="inlineStr">
+        <is>
+          <t>【種別：指定避難所】【対応災害：洪水, 崖崩れ・土石流, 地震】【所在地：大分県日田市天瀬町出口1840-1】【連絡先：(0973)57-2762】</t>
+        </is>
+      </c>
+      <c r="H116" t="n">
+        <v>0</v>
+      </c>
+      <c r="I116" t="inlineStr">
+        <is>
+          <t>待機中</t>
+        </is>
+      </c>
+      <c r="J116" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" t="n">
+        <v>116</v>
+      </c>
+      <c r="B117" t="inlineStr">
+        <is>
+          <t>いつま小学校</t>
+        </is>
+      </c>
+      <c r="C117" t="inlineStr">
+        <is>
+          <t>指定避難所</t>
+        </is>
+      </c>
+      <c r="D117" t="n">
+        <v>33.232984</v>
+      </c>
+      <c r="E117" t="n">
+        <v>131.019571</v>
+      </c>
+      <c r="F117" t="inlineStr">
+        <is>
+          <t>5分</t>
+        </is>
+      </c>
+      <c r="G117" t="inlineStr">
+        <is>
+          <t>【種別：指定避難所】【対応災害：洪水, 崖崩れ・土石流, 地震】【所在地：大分県日田市天瀬町五馬市2054-1】【連絡先：(0973)57-2750】</t>
+        </is>
+      </c>
+      <c r="H117" t="n">
+        <v>0</v>
+      </c>
+      <c r="I117" t="inlineStr">
+        <is>
+          <t>待機中</t>
+        </is>
+      </c>
+      <c r="J117" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" t="n">
+        <v>117</v>
+      </c>
+      <c r="B118" t="inlineStr">
+        <is>
+          <t>東渓中学校</t>
+        </is>
+      </c>
+      <c r="C118" t="inlineStr">
+        <is>
+          <t>指定避難所</t>
+        </is>
+      </c>
+      <c r="D118" t="n">
+        <v>33.28717</v>
+      </c>
+      <c r="E118" t="n">
+        <v>131.005798</v>
+      </c>
+      <c r="F118" t="inlineStr">
+        <is>
+          <t>5分</t>
+        </is>
+      </c>
+      <c r="G118" t="inlineStr">
+        <is>
+          <t>【種別：指定避難所】【対応災害：崖崩れ・土石流, 地震】【所在地：大分県日田市天瀬町馬原2276-1】【連絡先：(0973)57-2506】</t>
+        </is>
+      </c>
+      <c r="H118" t="n">
+        <v>0</v>
+      </c>
+      <c r="I118" t="inlineStr">
+        <is>
+          <t>待機中</t>
+        </is>
+      </c>
+      <c r="J118" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" t="n">
+        <v>118</v>
+      </c>
+      <c r="B119" t="inlineStr">
+        <is>
+          <t>五馬中学校</t>
+        </is>
+      </c>
+      <c r="C119" t="inlineStr">
+        <is>
+          <t>指定避難所</t>
+        </is>
+      </c>
+      <c r="D119" t="n">
+        <v>33.219222</v>
+      </c>
+      <c r="E119" t="n">
+        <v>131.02667</v>
+      </c>
+      <c r="F119" t="inlineStr">
+        <is>
+          <t>5分</t>
+        </is>
+      </c>
+      <c r="G119" t="inlineStr">
+        <is>
+          <t>【種別：指定避難所】【対応災害：洪水, 崖崩れ・土石流, 地震】【所在地：大分県日田市天瀬町塚田169-2】【連絡先：(0973)57-2036】</t>
+        </is>
+      </c>
+      <c r="H119" t="n">
+        <v>0</v>
+      </c>
+      <c r="I119" t="inlineStr">
+        <is>
+          <t>待機中</t>
+        </is>
+      </c>
+      <c r="J119" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" t="n">
+        <v>119</v>
+      </c>
+      <c r="B120" t="inlineStr">
+        <is>
+          <t>天瀬複合施設</t>
+        </is>
+      </c>
+      <c r="C120" t="inlineStr">
+        <is>
+          <t>指定避難所</t>
+        </is>
+      </c>
+      <c r="D120" t="n">
+        <v>33.283581</v>
+      </c>
+      <c r="E120" t="n">
+        <v>131.007558</v>
+      </c>
+      <c r="F120" t="inlineStr">
+        <is>
+          <t>5分</t>
+        </is>
+      </c>
+      <c r="G120" t="inlineStr">
+        <is>
+          <t>【種別：指定避難所】【対応災害：地震】【所在地：大分県日田市天瀬町合田1986-2】【連絡先：(0973)57-3157】</t>
+        </is>
+      </c>
+      <c r="H120" t="n">
+        <v>0</v>
+      </c>
+      <c r="I120" t="inlineStr">
+        <is>
+          <t>待機中</t>
+        </is>
+      </c>
+      <c r="J120" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" t="n">
+        <v>120</v>
+      </c>
+      <c r="B121" t="inlineStr">
+        <is>
+          <t>天瀬公民館</t>
+        </is>
+      </c>
+      <c r="C121" t="inlineStr">
+        <is>
+          <t>指定避難所</t>
+        </is>
+      </c>
+      <c r="D121" t="n">
+        <v>33.255112</v>
+      </c>
+      <c r="E121" t="n">
+        <v>131.020671</v>
+      </c>
+      <c r="F121" t="inlineStr">
+        <is>
+          <t>5分</t>
+        </is>
+      </c>
+      <c r="G121" t="inlineStr">
+        <is>
+          <t>【種別：指定避難所】【対応災害：崖崩れ・土石流, 地震】【所在地：大分県日田市天瀬町桜竹671-2】【連絡先：(0973)57-8212】</t>
+        </is>
+      </c>
+      <c r="H121" t="n">
+        <v>0</v>
+      </c>
+      <c r="I121" t="inlineStr">
+        <is>
+          <t>待機中</t>
+        </is>
+      </c>
+      <c r="J121" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" t="n">
+        <v>121</v>
+      </c>
+      <c r="B122" t="inlineStr">
+        <is>
+          <t>Ｂ＆Ｇ天瀬海洋センター</t>
+        </is>
+      </c>
+      <c r="C122" t="inlineStr">
+        <is>
+          <t>指定避難所</t>
+        </is>
+      </c>
+      <c r="D122" t="n">
+        <v>33.246453</v>
+      </c>
+      <c r="E122" t="n">
+        <v>131.032452</v>
+      </c>
+      <c r="F122" t="inlineStr">
+        <is>
+          <t>5分</t>
+        </is>
+      </c>
+      <c r="G122" t="inlineStr">
+        <is>
+          <t>【種別：指定避難所】【対応災害：洪水, 崖崩れ・土石流, 地震】【所在地：大分県日田市天瀬町桜竹80-1】【連絡先：(0973)57-3999】</t>
+        </is>
+      </c>
+      <c r="H122" t="n">
+        <v>0</v>
+      </c>
+      <c r="I122" t="inlineStr">
+        <is>
+          <t>待機中</t>
+        </is>
+      </c>
+      <c r="J122" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" t="n">
+        <v>122</v>
+      </c>
+      <c r="B123" t="inlineStr">
+        <is>
+          <t>天瀬公民館五馬分館</t>
+        </is>
+      </c>
+      <c r="C123" t="inlineStr">
+        <is>
+          <t>指定避難所</t>
+        </is>
+      </c>
+      <c r="D123" t="n">
+        <v>33.283401</v>
+      </c>
+      <c r="E123" t="n">
+        <v>131.007182</v>
+      </c>
+      <c r="F123" t="inlineStr">
+        <is>
+          <t>5分</t>
+        </is>
+      </c>
+      <c r="G123" t="inlineStr">
+        <is>
+          <t>【種別：指定避難所】【対応災害：洪水, 崖崩れ・土石流, 地震】【所在地：大分県日田市天瀬町五馬市2166-1】【連絡先：(0973)57-2994】</t>
+        </is>
+      </c>
+      <c r="H123" t="n">
+        <v>0</v>
+      </c>
+      <c r="I123" t="inlineStr">
+        <is>
+          <t>待機中</t>
+        </is>
+      </c>
+      <c r="J123" t="n">
+        <v>5</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/spots_en.xlsx
+++ b/spots_en.xlsx
@@ -1371,7 +1371,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>烏宿神社（からとまりじんじゃ）</t>
+          <t>烏宿神社（からすじゅくじんじゃ）</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -1996,7 +1996,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J123"/>
+  <dimension ref="A1:G123"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2035,21 +2035,6 @@
           <t>説明</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
-        <is>
-          <t>収容人数</t>
-        </is>
-      </c>
-      <c r="I1" s="1" t="inlineStr">
-        <is>
-          <t>状態</t>
-        </is>
-      </c>
-      <c r="J1" s="1" t="inlineStr">
-        <is>
-          <t>所要時間</t>
-        </is>
-      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -2081,17 +2066,6 @@
           <t>【種別：指定緊急避難場所】【対応災害：地震】【所在地：大分県日田市中ノ島町559】</t>
         </is>
       </c>
-      <c r="H2" t="n">
-        <v>0</v>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>待機中</t>
-        </is>
-      </c>
-      <c r="J2" t="n">
-        <v>5</v>
-      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -2123,17 +2097,6 @@
           <t>【種別：指定緊急避難場所】【対応災害：地震】【所在地：大分県日田市中ノ島町608-3】</t>
         </is>
       </c>
-      <c r="H3" t="n">
-        <v>0</v>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>待機中</t>
-        </is>
-      </c>
-      <c r="J3" t="n">
-        <v>5</v>
-      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -2165,17 +2128,6 @@
           <t>【種別：指定緊急避難場所】【対応災害：地震】【所在地：大分県日田市中ノ島町685-13】【連絡先：(0973)24-2123】</t>
         </is>
       </c>
-      <c r="H4" t="n">
-        <v>0</v>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>待機中</t>
-        </is>
-      </c>
-      <c r="J4" t="n">
-        <v>5</v>
-      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -2207,17 +2159,6 @@
           <t>【種別：指定緊急避難場所】【対応災害：地震】【所在地：大分県日田市本町19】</t>
         </is>
       </c>
-      <c r="H5" t="n">
-        <v>0</v>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>待機中</t>
-        </is>
-      </c>
-      <c r="J5" t="n">
-        <v>5</v>
-      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -2249,17 +2190,6 @@
           <t>【種別：指定緊急避難場所】【対応災害：地震】【所在地：大分県日田市本町56】</t>
         </is>
       </c>
-      <c r="H6" t="n">
-        <v>0</v>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>待機中</t>
-        </is>
-      </c>
-      <c r="J6" t="n">
-        <v>5</v>
-      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -2291,17 +2221,6 @@
           <t>【種別：指定緊急避難場所】【対応災害：地震】【所在地：大分県日田市東町716-3】</t>
         </is>
       </c>
-      <c r="H7" t="n">
-        <v>0</v>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>待機中</t>
-        </is>
-      </c>
-      <c r="J7" t="n">
-        <v>5</v>
-      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -2333,17 +2252,6 @@
           <t>【種別：指定緊急避難場所】【対応災害：地震】【所在地：大分県日田市若宮町1233-4】</t>
         </is>
       </c>
-      <c r="H8" t="n">
-        <v>0</v>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>待機中</t>
-        </is>
-      </c>
-      <c r="J8" t="n">
-        <v>5</v>
-      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -2375,17 +2283,6 @@
           <t>【種別：指定緊急避難場所】【対応災害：地震】【所在地：大分県日田市南元町132】</t>
         </is>
       </c>
-      <c r="H9" t="n">
-        <v>0</v>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>待機中</t>
-        </is>
-      </c>
-      <c r="J9" t="n">
-        <v>5</v>
-      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -2417,17 +2314,6 @@
           <t>【種別：指定緊急避難場所】【対応災害：地震】【所在地：大分県日田市港町398-5】</t>
         </is>
       </c>
-      <c r="H10" t="n">
-        <v>0</v>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>待機中</t>
-        </is>
-      </c>
-      <c r="J10" t="n">
-        <v>5</v>
-      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -2459,17 +2345,6 @@
           <t>【種別：指定緊急避難場所】【対応災害：地震】【所在地：大分県日田市中城町224-1】</t>
         </is>
       </c>
-      <c r="H11" t="n">
-        <v>0</v>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>待機中</t>
-        </is>
-      </c>
-      <c r="J11" t="n">
-        <v>5</v>
-      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -2501,17 +2376,6 @@
           <t>【種別：指定緊急避難場所】【対応災害：地震】【所在地：大分県日田市城町一丁目305-1】</t>
         </is>
       </c>
-      <c r="H12" t="n">
-        <v>0</v>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>待機中</t>
-        </is>
-      </c>
-      <c r="J12" t="n">
-        <v>5</v>
-      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -2543,17 +2407,6 @@
           <t>【種別：指定緊急避難場所】【対応災害：地震】【所在地：大分県日田市丸山二丁目2-1】</t>
         </is>
       </c>
-      <c r="H13" t="n">
-        <v>0</v>
-      </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>待機中</t>
-        </is>
-      </c>
-      <c r="J13" t="n">
-        <v>5</v>
-      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2585,17 +2438,6 @@
           <t>【種別：指定緊急避難場所】【対応災害：地震】【所在地：大分県日田市田島一丁目143】</t>
         </is>
       </c>
-      <c r="H14" t="n">
-        <v>0</v>
-      </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>待機中</t>
-        </is>
-      </c>
-      <c r="J14" t="n">
-        <v>5</v>
-      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2627,17 +2469,6 @@
           <t>【種別：指定緊急避難場所】【対応災害：地震】【所在地：大分県日田市田島二丁目286】</t>
         </is>
       </c>
-      <c r="H15" t="n">
-        <v>0</v>
-      </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>待機中</t>
-        </is>
-      </c>
-      <c r="J15" t="n">
-        <v>5</v>
-      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2669,17 +2500,6 @@
           <t>【種別：指定緊急避難場所】【対応災害：地震】【所在地：大分県日田市田島一丁目606】</t>
         </is>
       </c>
-      <c r="H16" t="n">
-        <v>0</v>
-      </c>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>待機中</t>
-        </is>
-      </c>
-      <c r="J16" t="n">
-        <v>5</v>
-      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2711,17 +2531,6 @@
           <t>【種別：指定緊急避難場所】【対応災害：地震】【所在地：大分県日田市田島本町175】</t>
         </is>
       </c>
-      <c r="H17" t="n">
-        <v>0</v>
-      </c>
-      <c r="I17" t="inlineStr">
-        <is>
-          <t>待機中</t>
-        </is>
-      </c>
-      <c r="J17" t="n">
-        <v>5</v>
-      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2753,17 +2562,6 @@
           <t>【種別：指定緊急避難場所】【対応災害：地震】【所在地：大分県日田市下井手町20】</t>
         </is>
       </c>
-      <c r="H18" t="n">
-        <v>0</v>
-      </c>
-      <c r="I18" t="inlineStr">
-        <is>
-          <t>待機中</t>
-        </is>
-      </c>
-      <c r="J18" t="n">
-        <v>5</v>
-      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2795,17 +2593,6 @@
           <t>【種別：指定緊急避難場所】【対応災害：地震】【所在地：大分県日田市三芳小渕町73】</t>
         </is>
       </c>
-      <c r="H19" t="n">
-        <v>0</v>
-      </c>
-      <c r="I19" t="inlineStr">
-        <is>
-          <t>待機中</t>
-        </is>
-      </c>
-      <c r="J19" t="n">
-        <v>5</v>
-      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2837,17 +2624,6 @@
           <t>【種別：指定緊急避難場所】【対応災害：地震】【所在地：大分県日田市京町27-1】</t>
         </is>
       </c>
-      <c r="H20" t="n">
-        <v>0</v>
-      </c>
-      <c r="I20" t="inlineStr">
-        <is>
-          <t>待機中</t>
-        </is>
-      </c>
-      <c r="J20" t="n">
-        <v>5</v>
-      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2879,17 +2655,6 @@
           <t>【種別：指定緊急避難場所】【対応災害：地震】【所在地：大分県日田市上野町393-1】</t>
         </is>
       </c>
-      <c r="H21" t="n">
-        <v>0</v>
-      </c>
-      <c r="I21" t="inlineStr">
-        <is>
-          <t>待機中</t>
-        </is>
-      </c>
-      <c r="J21" t="n">
-        <v>5</v>
-      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -2921,17 +2686,6 @@
           <t>【種別：指定緊急避難場所】【対応災害：地震】【所在地：大分県日田市小山479-1】</t>
         </is>
       </c>
-      <c r="H22" t="n">
-        <v>0</v>
-      </c>
-      <c r="I22" t="inlineStr">
-        <is>
-          <t>待機中</t>
-        </is>
-      </c>
-      <c r="J22" t="n">
-        <v>5</v>
-      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -2963,17 +2717,6 @@
           <t>【種別：指定緊急避難場所】【対応災害：地震】【所在地：大分県日田市北友田二丁目1950-1】</t>
         </is>
       </c>
-      <c r="H23" t="n">
-        <v>0</v>
-      </c>
-      <c r="I23" t="inlineStr">
-        <is>
-          <t>待機中</t>
-        </is>
-      </c>
-      <c r="J23" t="n">
-        <v>5</v>
-      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -3005,17 +2748,6 @@
           <t>【種別：指定緊急避難場所】【対応災害：地震】【所在地：大分県日田市北友田三丁目2531-37】</t>
         </is>
       </c>
-      <c r="H24" t="n">
-        <v>0</v>
-      </c>
-      <c r="I24" t="inlineStr">
-        <is>
-          <t>待機中</t>
-        </is>
-      </c>
-      <c r="J24" t="n">
-        <v>5</v>
-      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3047,17 +2779,6 @@
           <t>【種別：指定緊急避難場所】【対応災害：地震】【所在地：大分県日田市友田2483-3】</t>
         </is>
       </c>
-      <c r="H25" t="n">
-        <v>0</v>
-      </c>
-      <c r="I25" t="inlineStr">
-        <is>
-          <t>待機中</t>
-        </is>
-      </c>
-      <c r="J25" t="n">
-        <v>5</v>
-      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -3089,17 +2810,6 @@
           <t>【種別：指定緊急避難場所】【対応災害：地震】【所在地：大分県日田市君迫町1335-1】</t>
         </is>
       </c>
-      <c r="H26" t="n">
-        <v>0</v>
-      </c>
-      <c r="I26" t="inlineStr">
-        <is>
-          <t>待機中</t>
-        </is>
-      </c>
-      <c r="J26" t="n">
-        <v>5</v>
-      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -3131,17 +2841,6 @@
           <t>【種別：指定緊急避難場所】【対応災害：地震】【所在地：大分県日田市北友田1丁目1544-3】</t>
         </is>
       </c>
-      <c r="H27" t="n">
-        <v>0</v>
-      </c>
-      <c r="I27" t="inlineStr">
-        <is>
-          <t>待機中</t>
-        </is>
-      </c>
-      <c r="J27" t="n">
-        <v>5</v>
-      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -3173,17 +2872,6 @@
           <t>【種別：指定緊急避難場所】【対応災害：地震】【所在地：大分県日田市清水町1823-1】</t>
         </is>
       </c>
-      <c r="H28" t="n">
-        <v>0</v>
-      </c>
-      <c r="I28" t="inlineStr">
-        <is>
-          <t>待機中</t>
-        </is>
-      </c>
-      <c r="J28" t="n">
-        <v>5</v>
-      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -3215,17 +2903,6 @@
           <t>【種別：指定緊急避難場所】【対応災害：地震】【所在地：大分県日田市財津町2688-2】</t>
         </is>
       </c>
-      <c r="H29" t="n">
-        <v>0</v>
-      </c>
-      <c r="I29" t="inlineStr">
-        <is>
-          <t>待機中</t>
-        </is>
-      </c>
-      <c r="J29" t="n">
-        <v>5</v>
-      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -3257,17 +2934,6 @@
           <t>【種別：指定緊急避難場所】【対応災害：地震】【所在地：大分県日田市殿町3850-3】</t>
         </is>
       </c>
-      <c r="H30" t="n">
-        <v>0</v>
-      </c>
-      <c r="I30" t="inlineStr">
-        <is>
-          <t>待機中</t>
-        </is>
-      </c>
-      <c r="J30" t="n">
-        <v>5</v>
-      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -3299,17 +2965,6 @@
           <t>【種別：指定緊急避難場所】【対応災害：地震】【所在地：大分県日田市諸留町51】</t>
         </is>
       </c>
-      <c r="H31" t="n">
-        <v>0</v>
-      </c>
-      <c r="I31" t="inlineStr">
-        <is>
-          <t>待機中</t>
-        </is>
-      </c>
-      <c r="J31" t="n">
-        <v>5</v>
-      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -3341,17 +2996,6 @@
           <t>【種別：指定緊急避難場所】【対応災害：地震】【所在地：大分県日田市大鶴本町884-1】</t>
         </is>
       </c>
-      <c r="H32" t="n">
-        <v>0</v>
-      </c>
-      <c r="I32" t="inlineStr">
-        <is>
-          <t>待機中</t>
-        </is>
-      </c>
-      <c r="J32" t="n">
-        <v>5</v>
-      </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -3383,17 +3027,6 @@
           <t>【種別：指定緊急避難場所】【対応災害：地震】【所在地：大分県日田市前津江町大野2230-2】</t>
         </is>
       </c>
-      <c r="H33" t="n">
-        <v>0</v>
-      </c>
-      <c r="I33" t="inlineStr">
-        <is>
-          <t>待機中</t>
-        </is>
-      </c>
-      <c r="J33" t="n">
-        <v>5</v>
-      </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -3425,17 +3058,6 @@
           <t>【種別：指定緊急避難場所】【対応災害：地震】【所在地：大分県日田市上津江町上野田68-2】</t>
         </is>
       </c>
-      <c r="H34" t="n">
-        <v>0</v>
-      </c>
-      <c r="I34" t="inlineStr">
-        <is>
-          <t>待機中</t>
-        </is>
-      </c>
-      <c r="J34" t="n">
-        <v>5</v>
-      </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -3467,17 +3089,6 @@
           <t>【種別：指定緊急避難場所】【対応災害：地震】【所在地：大分県日田市大山町西大山8344-2】</t>
         </is>
       </c>
-      <c r="H35" t="n">
-        <v>0</v>
-      </c>
-      <c r="I35" t="inlineStr">
-        <is>
-          <t>待機中</t>
-        </is>
-      </c>
-      <c r="J35" t="n">
-        <v>5</v>
-      </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
@@ -3509,17 +3120,6 @@
           <t>【種別：指定避難所】【対応災害：洪水, 崖崩れ・土石流, 地震】【所在地：大分県日田市淡窓一丁目5-13】【連絡先：(0973)23-6292】</t>
         </is>
       </c>
-      <c r="H36" t="n">
-        <v>0</v>
-      </c>
-      <c r="I36" t="inlineStr">
-        <is>
-          <t>待機中</t>
-        </is>
-      </c>
-      <c r="J36" t="n">
-        <v>5</v>
-      </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
@@ -3551,17 +3151,6 @@
           <t>【種別：指定避難所】【対応災害：洪水, 崖崩れ・土石流, 地震】【所在地：大分県日田市淡窓一丁目5-31】【連絡先：(0973)22-5191】</t>
         </is>
       </c>
-      <c r="H37" t="n">
-        <v>0</v>
-      </c>
-      <c r="I37" t="inlineStr">
-        <is>
-          <t>待機中</t>
-        </is>
-      </c>
-      <c r="J37" t="n">
-        <v>5</v>
-      </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
@@ -3593,17 +3182,6 @@
           <t>【種別：指定避難所】【対応災害：洪水, 崖崩れ・土石流, 地震】【所在地：大分県日田市三本松一丁目8番11号】【連絡先：(0973)25-5000】</t>
         </is>
       </c>
-      <c r="H38" t="n">
-        <v>0</v>
-      </c>
-      <c r="I38" t="inlineStr">
-        <is>
-          <t>待機中</t>
-        </is>
-      </c>
-      <c r="J38" t="n">
-        <v>5</v>
-      </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
@@ -3635,17 +3213,6 @@
           <t>【種別：指定避難所】【対応災害：洪水, 崖崩れ・土石流, 地震】【所在地：大分県日田市上城内町2-35】【連絡先：(0973)24-6081】</t>
         </is>
       </c>
-      <c r="H39" t="n">
-        <v>0</v>
-      </c>
-      <c r="I39" t="inlineStr">
-        <is>
-          <t>待機中</t>
-        </is>
-      </c>
-      <c r="J39" t="n">
-        <v>5</v>
-      </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
@@ -3677,17 +3244,6 @@
           <t>【種別：指定避難所】【対応災害：洪水, 崖崩れ・土石流, 地震】【所在地：大分県日田市上城内町2-6】【連絡先：(0973)22-6868】</t>
         </is>
       </c>
-      <c r="H40" t="n">
-        <v>0</v>
-      </c>
-      <c r="I40" t="inlineStr">
-        <is>
-          <t>待機中</t>
-        </is>
-      </c>
-      <c r="J40" t="n">
-        <v>5</v>
-      </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
@@ -3719,17 +3275,6 @@
           <t>【種別：指定避難所】【対応災害：洪水, 崖崩れ・土石流, 地震】【所在地：大分県日田市上城内町2-11】【連絡先：(0973)24-3131】</t>
         </is>
       </c>
-      <c r="H41" t="n">
-        <v>0</v>
-      </c>
-      <c r="I41" t="inlineStr">
-        <is>
-          <t>待機中</t>
-        </is>
-      </c>
-      <c r="J41" t="n">
-        <v>5</v>
-      </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
@@ -3761,17 +3306,6 @@
           <t>【種別：指定避難所】【対応災害：洪水, 崖崩れ・土石流, 地震】【所在地：大分県日田市田島二丁目12-8】【連絡先：(0973)22-7135】</t>
         </is>
       </c>
-      <c r="H42" t="n">
-        <v>0</v>
-      </c>
-      <c r="I42" t="inlineStr">
-        <is>
-          <t>待機中</t>
-        </is>
-      </c>
-      <c r="J42" t="n">
-        <v>5</v>
-      </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
@@ -3803,17 +3337,6 @@
           <t>【種別：指定避難所】【対応災害：洪水, 崖崩れ・土石流, 地震】【所在地：大分県日田市田島二丁目9-30】【連絡先：(0973)23-0166】</t>
         </is>
       </c>
-      <c r="H43" t="n">
-        <v>0</v>
-      </c>
-      <c r="I43" t="inlineStr">
-        <is>
-          <t>待機中</t>
-        </is>
-      </c>
-      <c r="J43" t="n">
-        <v>5</v>
-      </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
@@ -3845,17 +3368,6 @@
           <t>【種別：指定避難所】【対応災害：洪水, 崖崩れ・土石流, 地震】【所在地：大分県日田市田島本町5-41】【連絡先：(0973)24-2737】</t>
         </is>
       </c>
-      <c r="H44" t="n">
-        <v>0</v>
-      </c>
-      <c r="I44" t="inlineStr">
-        <is>
-          <t>待機中</t>
-        </is>
-      </c>
-      <c r="J44" t="n">
-        <v>5</v>
-      </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
@@ -3887,17 +3399,6 @@
           <t>【種別：指定避難所】【対応災害：洪水, 崖崩れ・土石流, 地震】【所在地：大分県日田市田島三丁目29】【連絡先：(0973)24-6750】</t>
         </is>
       </c>
-      <c r="H45" t="n">
-        <v>0</v>
-      </c>
-      <c r="I45" t="inlineStr">
-        <is>
-          <t>待機中</t>
-        </is>
-      </c>
-      <c r="J45" t="n">
-        <v>5</v>
-      </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
@@ -3929,17 +3430,6 @@
           <t>【種別：指定避難所】【対応災害：洪水, 崖崩れ・土石流, 地震】【所在地：大分県日田市田島三丁目69】【連絡先：(0973)22-5733】</t>
         </is>
       </c>
-      <c r="H46" t="n">
-        <v>0</v>
-      </c>
-      <c r="I46" t="inlineStr">
-        <is>
-          <t>待機中</t>
-        </is>
-      </c>
-      <c r="J46" t="n">
-        <v>5</v>
-      </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
@@ -3971,17 +3461,6 @@
           <t>【種別：指定避難所】【対応災害：崖崩れ・土石流, 地震】【所在地：大分県日田市日ノ隈町578-1】【連絡先：(0973)23-6285】</t>
         </is>
       </c>
-      <c r="H47" t="n">
-        <v>0</v>
-      </c>
-      <c r="I47" t="inlineStr">
-        <is>
-          <t>待機中</t>
-        </is>
-      </c>
-      <c r="J47" t="n">
-        <v>5</v>
-      </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
@@ -4013,17 +3492,6 @@
           <t>【種別：指定避難所】【対応災害：洪水, 崖崩れ・土石流, 地震】【所在地：大分県日田市日ノ隈町515-1】【連絡先：(0973)22-6982】</t>
         </is>
       </c>
-      <c r="H48" t="n">
-        <v>0</v>
-      </c>
-      <c r="I48" t="inlineStr">
-        <is>
-          <t>待機中</t>
-        </is>
-      </c>
-      <c r="J48" t="n">
-        <v>5</v>
-      </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
@@ -4055,17 +3523,6 @@
           <t>【種別：指定避難所】【対応災害：崖崩れ・土石流, 地震】【所在地：大分県日田市亀川町402-1】【連絡先：(0973)23-6237】</t>
         </is>
       </c>
-      <c r="H49" t="n">
-        <v>0</v>
-      </c>
-      <c r="I49" t="inlineStr">
-        <is>
-          <t>待機中</t>
-        </is>
-      </c>
-      <c r="J49" t="n">
-        <v>5</v>
-      </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
@@ -4097,17 +3554,6 @@
           <t>【種別：指定避難所】【対応災害：崖崩れ・土石流, 地震】【所在地：大分県日田市若宮町2-15】【連絡先：(0973)23-6282】</t>
         </is>
       </c>
-      <c r="H50" t="n">
-        <v>0</v>
-      </c>
-      <c r="I50" t="inlineStr">
-        <is>
-          <t>待機中</t>
-        </is>
-      </c>
-      <c r="J50" t="n">
-        <v>5</v>
-      </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
@@ -4139,17 +3585,6 @@
           <t>【種別：指定避難所】【対応災害：洪水, 崖崩れ・土石流, 地震】【所在地：大分県日田市竹田新町1-37】【連絡先：(0973)23-9850】</t>
         </is>
       </c>
-      <c r="H51" t="n">
-        <v>0</v>
-      </c>
-      <c r="I51" t="inlineStr">
-        <is>
-          <t>待機中</t>
-        </is>
-      </c>
-      <c r="J51" t="n">
-        <v>5</v>
-      </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
@@ -4181,17 +3616,6 @@
           <t>【種別：指定避難所】【対応災害：崖崩れ・土石流, 地震】【所在地：大分県日田市下井手町989】【連絡先：(0973)22-1491】</t>
         </is>
       </c>
-      <c r="H52" t="n">
-        <v>0</v>
-      </c>
-      <c r="I52" t="inlineStr">
-        <is>
-          <t>待機中</t>
-        </is>
-      </c>
-      <c r="J52" t="n">
-        <v>5</v>
-      </c>
     </row>
     <row r="53">
       <c r="A53" t="n">
@@ -4223,17 +3647,6 @@
           <t>【種別：指定避難所】【対応災害：崖崩れ・土石流, 地震】【所在地：大分県日田市下井手町940】【連絡先：(0973)23-6234】</t>
         </is>
       </c>
-      <c r="H53" t="n">
-        <v>0</v>
-      </c>
-      <c r="I53" t="inlineStr">
-        <is>
-          <t>待機中</t>
-        </is>
-      </c>
-      <c r="J53" t="n">
-        <v>5</v>
-      </c>
     </row>
     <row r="54">
       <c r="A54" t="n">
@@ -4265,17 +3678,6 @@
           <t>【種別：指定避難所】【対応災害：洪水, 崖崩れ・土石流, 地震】【所在地：大分県日田市銭渕町288】【連絡先：(0973)23-6275】</t>
         </is>
       </c>
-      <c r="H54" t="n">
-        <v>0</v>
-      </c>
-      <c r="I54" t="inlineStr">
-        <is>
-          <t>待機中</t>
-        </is>
-      </c>
-      <c r="J54" t="n">
-        <v>5</v>
-      </c>
     </row>
     <row r="55">
       <c r="A55" t="n">
@@ -4307,17 +3709,6 @@
           <t>【種別：指定避難所】【対応災害：洪水, 崖崩れ・土石流, 地震】【所在地：大分県日田市誠和町781-2】【連絡先：(0973)23-6241】</t>
         </is>
       </c>
-      <c r="H55" t="n">
-        <v>0</v>
-      </c>
-      <c r="I55" t="inlineStr">
-        <is>
-          <t>待機中</t>
-        </is>
-      </c>
-      <c r="J55" t="n">
-        <v>5</v>
-      </c>
     </row>
     <row r="56">
       <c r="A56" t="n">
@@ -4349,17 +3740,6 @@
           <t>【種別：指定避難所】【対応災害：洪水, 崖崩れ・土石流, 地震】【所在地：大分県日田市誠和町796-3】【連絡先：(0973)24-2705】</t>
         </is>
       </c>
-      <c r="H56" t="n">
-        <v>0</v>
-      </c>
-      <c r="I56" t="inlineStr">
-        <is>
-          <t>待機中</t>
-        </is>
-      </c>
-      <c r="J56" t="n">
-        <v>5</v>
-      </c>
     </row>
     <row r="57">
       <c r="A57" t="n">
@@ -4391,17 +3771,6 @@
           <t>【種別：指定避難所】【対応災害：崖崩れ・土石流, 地震】【所在地：大分県日田市吹上町30】【連絡先：(0973)22-5171】</t>
         </is>
       </c>
-      <c r="H57" t="n">
-        <v>0</v>
-      </c>
-      <c r="I57" t="inlineStr">
-        <is>
-          <t>待機中</t>
-        </is>
-      </c>
-      <c r="J57" t="n">
-        <v>5</v>
-      </c>
     </row>
     <row r="58">
       <c r="A58" t="n">
@@ -4433,17 +3802,6 @@
           <t>【種別：指定避難所】【対応災害：地震】【所在地：大分県日田市北友田一丁目1133-2】【連絡先：(0973)23-6258】</t>
         </is>
       </c>
-      <c r="H58" t="n">
-        <v>0</v>
-      </c>
-      <c r="I58" t="inlineStr">
-        <is>
-          <t>待機中</t>
-        </is>
-      </c>
-      <c r="J58" t="n">
-        <v>5</v>
-      </c>
     </row>
     <row r="59">
       <c r="A59" t="n">
@@ -4475,17 +3833,6 @@
           <t>【種別：指定避難所】【対応災害：崖崩れ・土石流, 地震】【所在地：大分県日田市北友田一丁目1221-1】【連絡先：(0973)23-8984】</t>
         </is>
       </c>
-      <c r="H59" t="n">
-        <v>0</v>
-      </c>
-      <c r="I59" t="inlineStr">
-        <is>
-          <t>待機中</t>
-        </is>
-      </c>
-      <c r="J59" t="n">
-        <v>5</v>
-      </c>
     </row>
     <row r="60">
       <c r="A60" t="n">
@@ -4517,17 +3864,6 @@
           <t>【種別：指定避難所】【対応災害：洪水, 崖崩れ・土石流, 地震】【所在地：大分県日田市友田1546-1】【連絡先：(0973)23-3130】</t>
         </is>
       </c>
-      <c r="H60" t="n">
-        <v>0</v>
-      </c>
-      <c r="I60" t="inlineStr">
-        <is>
-          <t>待機中</t>
-        </is>
-      </c>
-      <c r="J60" t="n">
-        <v>5</v>
-      </c>
     </row>
     <row r="61">
       <c r="A61" t="n">
@@ -4559,17 +3895,6 @@
           <t>【種別：指定避難所】【対応災害：崖崩れ・土石流, 地震】【所在地：大分県日田市南友田町717-1】【連絡先：(0973)24-3350】</t>
         </is>
       </c>
-      <c r="H61" t="n">
-        <v>0</v>
-      </c>
-      <c r="I61" t="inlineStr">
-        <is>
-          <t>待機中</t>
-        </is>
-      </c>
-      <c r="J61" t="n">
-        <v>5</v>
-      </c>
     </row>
     <row r="62">
       <c r="A62" t="n">
@@ -4601,17 +3926,6 @@
           <t>【種別：指定避難所】【対応災害：崖崩れ・土石流, 地震】【所在地：大分県日田市日ノ出町14】【連絡先：(0973)22-7420】</t>
         </is>
       </c>
-      <c r="H62" t="n">
-        <v>0</v>
-      </c>
-      <c r="I62" t="inlineStr">
-        <is>
-          <t>待機中</t>
-        </is>
-      </c>
-      <c r="J62" t="n">
-        <v>5</v>
-      </c>
     </row>
     <row r="63">
       <c r="A63" t="n">
@@ -4643,17 +3957,6 @@
           <t>【種別：指定避難所】【対応災害：洪水, 崖崩れ・土石流, 地震】【所在地：大分県日田市朝日町936-1】【連絡先：(0973)22-5242】</t>
         </is>
       </c>
-      <c r="H63" t="n">
-        <v>0</v>
-      </c>
-      <c r="I63" t="inlineStr">
-        <is>
-          <t>待機中</t>
-        </is>
-      </c>
-      <c r="J63" t="n">
-        <v>5</v>
-      </c>
     </row>
     <row r="64">
       <c r="A64" t="n">
@@ -4685,17 +3988,6 @@
           <t>【種別：指定避難所】【対応災害：洪水, 崖崩れ・土石流, 地震】【所在地：大分県日田市朝日町945-1】【連絡先：(0973)23-8994】</t>
         </is>
       </c>
-      <c r="H64" t="n">
-        <v>0</v>
-      </c>
-      <c r="I64" t="inlineStr">
-        <is>
-          <t>待機中</t>
-        </is>
-      </c>
-      <c r="J64" t="n">
-        <v>5</v>
-      </c>
     </row>
     <row r="65">
       <c r="A65" t="n">
@@ -4727,17 +4019,6 @@
           <t>【種別：指定避難所】【対応災害：洪水, 地震】【所在地：大分県日田市清水町1187】【連絡先：(0973)22-2284】</t>
         </is>
       </c>
-      <c r="H65" t="n">
-        <v>0</v>
-      </c>
-      <c r="I65" t="inlineStr">
-        <is>
-          <t>待機中</t>
-        </is>
-      </c>
-      <c r="J65" t="n">
-        <v>5</v>
-      </c>
     </row>
     <row r="66">
       <c r="A66" t="n">
@@ -4769,17 +4050,6 @@
           <t>【種別：指定避難所】【対応災害：洪水, 崖崩れ・土石流, 地震】【所在地：大分県日田市清水町948-1】【連絡先：(0973)24-3388】</t>
         </is>
       </c>
-      <c r="H66" t="n">
-        <v>0</v>
-      </c>
-      <c r="I66" t="inlineStr">
-        <is>
-          <t>待機中</t>
-        </is>
-      </c>
-      <c r="J66" t="n">
-        <v>5</v>
-      </c>
     </row>
     <row r="67">
       <c r="A67" t="n">
@@ -4811,17 +4081,6 @@
           <t>【種別：指定避難所】【対応災害：崖崩れ・土石流, 地震】【所在地：大分県日田市上手町148-1】【連絡先：(0973)23-6272】</t>
         </is>
       </c>
-      <c r="H67" t="n">
-        <v>0</v>
-      </c>
-      <c r="I67" t="inlineStr">
-        <is>
-          <t>待機中</t>
-        </is>
-      </c>
-      <c r="J67" t="n">
-        <v>5</v>
-      </c>
     </row>
     <row r="68">
       <c r="A68" t="n">
@@ -4853,17 +4112,6 @@
           <t>【種別：指定避難所】【対応災害：洪水, 崖崩れ・土石流, 地震】【所在地：大分県日田市大字花月1436-1】【連絡先：(0973)24-9403】</t>
         </is>
       </c>
-      <c r="H68" t="n">
-        <v>0</v>
-      </c>
-      <c r="I68" t="inlineStr">
-        <is>
-          <t>待機中</t>
-        </is>
-      </c>
-      <c r="J68" t="n">
-        <v>5</v>
-      </c>
     </row>
     <row r="69">
       <c r="A69" t="n">
@@ -4895,17 +4143,6 @@
           <t>【種別：指定避難所】【対応災害：洪水, 崖崩れ・土石流】【所在地：大分県日田市伏木町3512】【連絡先：(0973)24-9606】</t>
         </is>
       </c>
-      <c r="H69" t="n">
-        <v>0</v>
-      </c>
-      <c r="I69" t="inlineStr">
-        <is>
-          <t>待機中</t>
-        </is>
-      </c>
-      <c r="J69" t="n">
-        <v>5</v>
-      </c>
     </row>
     <row r="70">
       <c r="A70" t="n">
@@ -4937,17 +4174,6 @@
           <t>【種別：指定避難所】【対応災害：洪水, 地震】【所在地：大分県日田市藤山町213-1】【連絡先：(0973)24-9140】</t>
         </is>
       </c>
-      <c r="H70" t="n">
-        <v>0</v>
-      </c>
-      <c r="I70" t="inlineStr">
-        <is>
-          <t>待機中</t>
-        </is>
-      </c>
-      <c r="J70" t="n">
-        <v>5</v>
-      </c>
     </row>
     <row r="71">
       <c r="A71" t="n">
@@ -4979,17 +4205,6 @@
           <t>【種別：指定避難所】【対応災害：洪水, 地震】【所在地：大分県日田市鈴連町1658-1】【連絡先：(0973)29-2111】</t>
         </is>
       </c>
-      <c r="H71" t="n">
-        <v>0</v>
-      </c>
-      <c r="I71" t="inlineStr">
-        <is>
-          <t>待機中</t>
-        </is>
-      </c>
-      <c r="J71" t="n">
-        <v>5</v>
-      </c>
     </row>
     <row r="72">
       <c r="A72" t="n">
@@ -5021,17 +4236,6 @@
           <t>【種別：指定避難所】【対応災害：洪水, 崖崩れ・土石流, 地震】【所在地：大分県日田市鈴連町900-3】【連絡先：(0973)29-2201】</t>
         </is>
       </c>
-      <c r="H72" t="n">
-        <v>0</v>
-      </c>
-      <c r="I72" t="inlineStr">
-        <is>
-          <t>待機中</t>
-        </is>
-      </c>
-      <c r="J72" t="n">
-        <v>5</v>
-      </c>
     </row>
     <row r="73">
       <c r="A73" t="n">
@@ -5063,17 +4267,6 @@
           <t>【種別：指定避難所】【対応災害：洪水, 崖崩れ・土石流, 地震】【所在地：大分県日田市石松町2927-1】【連絡先：(0973)22-4702】</t>
         </is>
       </c>
-      <c r="H73" t="n">
-        <v>0</v>
-      </c>
-      <c r="I73" t="inlineStr">
-        <is>
-          <t>待機中</t>
-        </is>
-      </c>
-      <c r="J73" t="n">
-        <v>5</v>
-      </c>
     </row>
     <row r="74">
       <c r="A74" t="n">
@@ -5105,17 +4298,6 @@
           <t>【種別：指定避難所】【対応災害：洪水, 崖崩れ・土石流, 地震】【所在地：大分県日田市石松町2941-1】【連絡先：(0973)24-2000】</t>
         </is>
       </c>
-      <c r="H74" t="n">
-        <v>0</v>
-      </c>
-      <c r="I74" t="inlineStr">
-        <is>
-          <t>待機中</t>
-        </is>
-      </c>
-      <c r="J74" t="n">
-        <v>5</v>
-      </c>
     </row>
     <row r="75">
       <c r="A75" t="n">
@@ -5147,17 +4329,6 @@
           <t>【種別：指定避難所】【対応災害：崖崩れ・土石流, 地震】【所在地：大分県日田市諸留町2687-1】【連絡先：(0973)24-2175】</t>
         </is>
       </c>
-      <c r="H75" t="n">
-        <v>0</v>
-      </c>
-      <c r="I75" t="inlineStr">
-        <is>
-          <t>待機中</t>
-        </is>
-      </c>
-      <c r="J75" t="n">
-        <v>5</v>
-      </c>
     </row>
     <row r="76">
       <c r="A76" t="n">
@@ -5189,17 +4360,6 @@
           <t>【種別：指定避難所】【対応災害：地震】【所在地：大分県日田市諸留町488-2】【連絡先：(0973)24-8179】</t>
         </is>
       </c>
-      <c r="H76" t="n">
-        <v>0</v>
-      </c>
-      <c r="I76" t="inlineStr">
-        <is>
-          <t>待機中</t>
-        </is>
-      </c>
-      <c r="J76" t="n">
-        <v>5</v>
-      </c>
     </row>
     <row r="77">
       <c r="A77" t="n">
@@ -5231,17 +4391,6 @@
           <t>【種別：指定避難所】【対応災害：崖崩れ・土石流】【所在地：大分県日田市諸留町52】【連絡先：(0973)24-8111】</t>
         </is>
       </c>
-      <c r="H77" t="n">
-        <v>0</v>
-      </c>
-      <c r="I77" t="inlineStr">
-        <is>
-          <t>待機中</t>
-        </is>
-      </c>
-      <c r="J77" t="n">
-        <v>5</v>
-      </c>
     </row>
     <row r="78">
       <c r="A78" t="n">
@@ -5273,17 +4422,6 @@
           <t>【種別：指定避難所】【対応災害：洪水, 崖崩れ・土石流, 地震】【所在地：大分県日田市日の本町2463-1】【連絡先：(0973)24-8421】</t>
         </is>
       </c>
-      <c r="H78" t="n">
-        <v>0</v>
-      </c>
-      <c r="I78" t="inlineStr">
-        <is>
-          <t>待機中</t>
-        </is>
-      </c>
-      <c r="J78" t="n">
-        <v>5</v>
-      </c>
     </row>
     <row r="79">
       <c r="A79" t="n">
@@ -5315,17 +4453,6 @@
           <t>【種別：指定避難所】【対応災害：洪水, 崖崩れ・土石流, 地震】【所在地：大分県日田市月出町5590】【連絡先：(0973)24-8767】</t>
         </is>
       </c>
-      <c r="H79" t="n">
-        <v>0</v>
-      </c>
-      <c r="I79" t="inlineStr">
-        <is>
-          <t>待機中</t>
-        </is>
-      </c>
-      <c r="J79" t="n">
-        <v>5</v>
-      </c>
     </row>
     <row r="80">
       <c r="A80" t="n">
@@ -5357,17 +4484,6 @@
           <t>【種別：指定避難所】【対応災害：洪水, 地震】【所在地：大分県日田市大肥本町1701】【連絡先：(0973)28-2224】</t>
         </is>
       </c>
-      <c r="H80" t="n">
-        <v>0</v>
-      </c>
-      <c r="I80" t="inlineStr">
-        <is>
-          <t>待機中</t>
-        </is>
-      </c>
-      <c r="J80" t="n">
-        <v>5</v>
-      </c>
     </row>
     <row r="81">
       <c r="A81" t="n">
@@ -5399,17 +4515,6 @@
           <t>【種別：指定避難所】【対応災害：洪水, 崖崩れ・土石流, 地震】【所在地：大分県日田市大鶴本町870】【連絡先：(0973)28-2121】</t>
         </is>
       </c>
-      <c r="H81" t="n">
-        <v>0</v>
-      </c>
-      <c r="I81" t="inlineStr">
-        <is>
-          <t>待機中</t>
-        </is>
-      </c>
-      <c r="J81" t="n">
-        <v>5</v>
-      </c>
     </row>
     <row r="82">
       <c r="A82" t="n">
@@ -5441,17 +4546,6 @@
           <t>【種別：指定避難所】【対応災害：洪水, 崖崩れ・土石流, 地震】【所在地：大分県日田市夜明中町1547】【連絡先：(0973)27-2121】</t>
         </is>
       </c>
-      <c r="H82" t="n">
-        <v>0</v>
-      </c>
-      <c r="I82" t="inlineStr">
-        <is>
-          <t>待機中</t>
-        </is>
-      </c>
-      <c r="J82" t="n">
-        <v>5</v>
-      </c>
     </row>
     <row r="83">
       <c r="A83" t="n">
@@ -5483,17 +4577,6 @@
           <t>【種別：指定避難所】【対応災害：崖崩れ・土石流, 地震】【所在地：大分県日田市石井町二丁目478】【連絡先：(0973)22-3442】</t>
         </is>
       </c>
-      <c r="H83" t="n">
-        <v>0</v>
-      </c>
-      <c r="I83" t="inlineStr">
-        <is>
-          <t>待機中</t>
-        </is>
-      </c>
-      <c r="J83" t="n">
-        <v>5</v>
-      </c>
     </row>
     <row r="84">
       <c r="A84" t="n">
@@ -5525,17 +4608,6 @@
           <t>【種別：指定避難所】【対応災害：洪水, 崖崩れ・土石流, 地震】【所在地：大分県日田市石井町一丁目274-4】【連絡先：(0973)22-4126】</t>
         </is>
       </c>
-      <c r="H84" t="n">
-        <v>0</v>
-      </c>
-      <c r="I84" t="inlineStr">
-        <is>
-          <t>待機中</t>
-        </is>
-      </c>
-      <c r="J84" t="n">
-        <v>5</v>
-      </c>
     </row>
     <row r="85">
       <c r="A85" t="n">
@@ -5567,17 +4639,6 @@
           <t>【種別：指定避難所】【対応災害：洪水, 地震】【所在地：大分県日田市前津江町柚木451】</t>
         </is>
       </c>
-      <c r="H85" t="n">
-        <v>0</v>
-      </c>
-      <c r="I85" t="inlineStr">
-        <is>
-          <t>待機中</t>
-        </is>
-      </c>
-      <c r="J85" t="n">
-        <v>5</v>
-      </c>
     </row>
     <row r="86">
       <c r="A86" t="n">
@@ -5609,17 +4670,6 @@
           <t>【種別：指定避難所】【対応災害：洪水, 崖崩れ・土石流, 地震】【所在地：大分県日田市前津江町柚木2194-1】</t>
         </is>
       </c>
-      <c r="H86" t="n">
-        <v>0</v>
-      </c>
-      <c r="I86" t="inlineStr">
-        <is>
-          <t>待機中</t>
-        </is>
-      </c>
-      <c r="J86" t="n">
-        <v>5</v>
-      </c>
     </row>
     <row r="87">
       <c r="A87" t="n">
@@ -5651,17 +4701,6 @@
           <t>【種別：指定避難所】【対応災害：洪水, 地震】【所在地：大分県日田市前津江町大野2562】【連絡先：(0973)53-2210】</t>
         </is>
       </c>
-      <c r="H87" t="n">
-        <v>0</v>
-      </c>
-      <c r="I87" t="inlineStr">
-        <is>
-          <t>待機中</t>
-        </is>
-      </c>
-      <c r="J87" t="n">
-        <v>5</v>
-      </c>
     </row>
     <row r="88">
       <c r="A88" t="n">
@@ -5693,17 +4732,6 @@
           <t>【種別：指定避難所】【対応災害：洪水, 地震】【所在地：大分県日田市前津江町赤石3121-2】</t>
         </is>
       </c>
-      <c r="H88" t="n">
-        <v>0</v>
-      </c>
-      <c r="I88" t="inlineStr">
-        <is>
-          <t>待機中</t>
-        </is>
-      </c>
-      <c r="J88" t="n">
-        <v>5</v>
-      </c>
     </row>
     <row r="89">
       <c r="A89" t="n">
@@ -5735,17 +4763,6 @@
           <t>【種別：指定避難所】【対応災害：洪水, 地震】【所在地：大分県日田市前津江町大野2214】【連絡先：(0973)53-2211】</t>
         </is>
       </c>
-      <c r="H89" t="n">
-        <v>0</v>
-      </c>
-      <c r="I89" t="inlineStr">
-        <is>
-          <t>待機中</t>
-        </is>
-      </c>
-      <c r="J89" t="n">
-        <v>5</v>
-      </c>
     </row>
     <row r="90">
       <c r="A90" t="n">
@@ -5777,17 +4794,6 @@
           <t>【種別：指定避難所】【対応災害：洪水, 崖崩れ・土石流, 地震】【所在地：大分県日田市前津江町柚木2185-1】【連絡先：(0973)53-2162】</t>
         </is>
       </c>
-      <c r="H90" t="n">
-        <v>0</v>
-      </c>
-      <c r="I90" t="inlineStr">
-        <is>
-          <t>待機中</t>
-        </is>
-      </c>
-      <c r="J90" t="n">
-        <v>5</v>
-      </c>
     </row>
     <row r="91">
       <c r="A91" t="n">
@@ -5819,17 +4825,6 @@
           <t>【種別：指定避難所】【対応災害：洪水, 崖崩れ・土石流, 地震】【所在地：大分県日田市前津江町大野70-15】【連絡先：(0973)53-2041】</t>
         </is>
       </c>
-      <c r="H91" t="n">
-        <v>0</v>
-      </c>
-      <c r="I91" t="inlineStr">
-        <is>
-          <t>待機中</t>
-        </is>
-      </c>
-      <c r="J91" t="n">
-        <v>5</v>
-      </c>
     </row>
     <row r="92">
       <c r="A92" t="n">
@@ -5861,17 +4856,6 @@
           <t>【種別：指定避難所】【対応災害：洪水, 地震】【所在地：大分県日田市前津江町大野2188】【連絡先：(0973)53-2409】</t>
         </is>
       </c>
-      <c r="H92" t="n">
-        <v>0</v>
-      </c>
-      <c r="I92" t="inlineStr">
-        <is>
-          <t>待機中</t>
-        </is>
-      </c>
-      <c r="J92" t="n">
-        <v>5</v>
-      </c>
     </row>
     <row r="93">
       <c r="A93" t="n">
@@ -5903,17 +4887,6 @@
           <t>【種別：指定避難所】【対応災害：洪水, 地震】【所在地：大分県日田市前津江町大野2179-2】【連絡先：(0973)53-2111】</t>
         </is>
       </c>
-      <c r="H93" t="n">
-        <v>0</v>
-      </c>
-      <c r="I93" t="inlineStr">
-        <is>
-          <t>待機中</t>
-        </is>
-      </c>
-      <c r="J93" t="n">
-        <v>5</v>
-      </c>
     </row>
     <row r="94">
       <c r="A94" t="n">
@@ -5945,17 +4918,6 @@
           <t>【種別：指定避難所】【対応災害：洪水】【所在地：大分県日田市前津江町赤石1932-1】</t>
         </is>
       </c>
-      <c r="H94" t="n">
-        <v>0</v>
-      </c>
-      <c r="I94" t="inlineStr">
-        <is>
-          <t>待機中</t>
-        </is>
-      </c>
-      <c r="J94" t="n">
-        <v>5</v>
-      </c>
     </row>
     <row r="95">
       <c r="A95" t="n">
@@ -5987,17 +4949,6 @@
           <t>【種別：指定避難所】【対応災害：洪水, 地震】【所在地：大分県日田市中津江村栃野2357-1】【連絡先：(0973)54-3111】</t>
         </is>
       </c>
-      <c r="H95" t="n">
-        <v>0</v>
-      </c>
-      <c r="I95" t="inlineStr">
-        <is>
-          <t>待機中</t>
-        </is>
-      </c>
-      <c r="J95" t="n">
-        <v>5</v>
-      </c>
     </row>
     <row r="96">
       <c r="A96" t="n">
@@ -6029,17 +4980,6 @@
           <t>【種別：指定避難所】【対応災害：洪水, 崖崩れ・土石流, 地震】【所在地：大分県日田市中津江村栃野4341】【連絡先：(0973)54-3116】</t>
         </is>
       </c>
-      <c r="H96" t="n">
-        <v>0</v>
-      </c>
-      <c r="I96" t="inlineStr">
-        <is>
-          <t>待機中</t>
-        </is>
-      </c>
-      <c r="J96" t="n">
-        <v>5</v>
-      </c>
     </row>
     <row r="97">
       <c r="A97" t="n">
@@ -6071,17 +5011,6 @@
           <t>【種別：指定避難所】【対応災害：洪水, 崖崩れ・土石流, 地震】【所在地：大分県日田市中津江村合瀬1936-28】【連絡先：(0973)56-5016】</t>
         </is>
       </c>
-      <c r="H97" t="n">
-        <v>0</v>
-      </c>
-      <c r="I97" t="inlineStr">
-        <is>
-          <t>待機中</t>
-        </is>
-      </c>
-      <c r="J97" t="n">
-        <v>5</v>
-      </c>
     </row>
     <row r="98">
       <c r="A98" t="n">
@@ -6113,17 +5042,6 @@
           <t>【種別：指定避難所】【対応災害：洪水】【所在地：大分県日田市中津江村合瀬3750】【連絡先：(0973)56-5316】</t>
         </is>
       </c>
-      <c r="H98" t="n">
-        <v>0</v>
-      </c>
-      <c r="I98" t="inlineStr">
-        <is>
-          <t>待機中</t>
-        </is>
-      </c>
-      <c r="J98" t="n">
-        <v>5</v>
-      </c>
     </row>
     <row r="99">
       <c r="A99" t="n">
@@ -6155,17 +5073,6 @@
           <t>【種別：指定避難所】【対応災害：洪水, 崖崩れ・土石流, 地震】【所在地：大分県日田市上津江町川原2710】【連絡先：(0973)55-2011】</t>
         </is>
       </c>
-      <c r="H99" t="n">
-        <v>0</v>
-      </c>
-      <c r="I99" t="inlineStr">
-        <is>
-          <t>待機中</t>
-        </is>
-      </c>
-      <c r="J99" t="n">
-        <v>5</v>
-      </c>
     </row>
     <row r="100">
       <c r="A100" t="n">
@@ -6197,17 +5104,6 @@
           <t>【種別：指定避難所】【対応災害：洪水, 地震】【所在地：大分県日田市上津江町上野田1217-9】</t>
         </is>
       </c>
-      <c r="H100" t="n">
-        <v>0</v>
-      </c>
-      <c r="I100" t="inlineStr">
-        <is>
-          <t>待機中</t>
-        </is>
-      </c>
-      <c r="J100" t="n">
-        <v>5</v>
-      </c>
     </row>
     <row r="101">
       <c r="A101" t="n">
@@ -6239,17 +5135,6 @@
           <t>【種別：指定避難所】【対応災害：洪水】【所在地：大分県日田市上津江町川原3852-1】</t>
         </is>
       </c>
-      <c r="H101" t="n">
-        <v>0</v>
-      </c>
-      <c r="I101" t="inlineStr">
-        <is>
-          <t>待機中</t>
-        </is>
-      </c>
-      <c r="J101" t="n">
-        <v>5</v>
-      </c>
     </row>
     <row r="102">
       <c r="A102" t="n">
@@ -6281,17 +5166,6 @@
           <t>【種別：指定避難所】【対応災害：洪水, 崖崩れ・土石流, 地震】【所在地：大分県日田市大山町西大山5926-3】</t>
         </is>
       </c>
-      <c r="H102" t="n">
-        <v>0</v>
-      </c>
-      <c r="I102" t="inlineStr">
-        <is>
-          <t>待機中</t>
-        </is>
-      </c>
-      <c r="J102" t="n">
-        <v>5</v>
-      </c>
     </row>
     <row r="103">
       <c r="A103" t="n">
@@ -6323,17 +5197,6 @@
           <t>【種別：指定避難所】【対応災害：洪水, 崖崩れ・土石流, 地震】【所在地：大分県日田市大山町東大山1125】【連絡先：(0973)52-3006】</t>
         </is>
       </c>
-      <c r="H103" t="n">
-        <v>0</v>
-      </c>
-      <c r="I103" t="inlineStr">
-        <is>
-          <t>待機中</t>
-        </is>
-      </c>
-      <c r="J103" t="n">
-        <v>5</v>
-      </c>
     </row>
     <row r="104">
       <c r="A104" t="n">
@@ -6365,17 +5228,6 @@
           <t>【種別：指定避難所】【対応災害：洪水】【所在地：大分県日田市大山町西大山4267】</t>
         </is>
       </c>
-      <c r="H104" t="n">
-        <v>0</v>
-      </c>
-      <c r="I104" t="inlineStr">
-        <is>
-          <t>待機中</t>
-        </is>
-      </c>
-      <c r="J104" t="n">
-        <v>5</v>
-      </c>
     </row>
     <row r="105">
       <c r="A105" t="n">
@@ -6407,17 +5259,6 @@
           <t>【種別：指定避難所】【対応災害：洪水】【所在地：大分県日田市大山町西大山8442-3】【連絡先：(0973)52-2922】</t>
         </is>
       </c>
-      <c r="H105" t="n">
-        <v>0</v>
-      </c>
-      <c r="I105" t="inlineStr">
-        <is>
-          <t>待機中</t>
-        </is>
-      </c>
-      <c r="J105" t="n">
-        <v>5</v>
-      </c>
     </row>
     <row r="106">
       <c r="A106" t="n">
@@ -6449,17 +5290,6 @@
           <t>【種別：指定避難所】【対応災害：洪水, 崖崩れ・土石流, 地震】【所在地：大分県日田市大山町西大山8504-1地先】</t>
         </is>
       </c>
-      <c r="H106" t="n">
-        <v>0</v>
-      </c>
-      <c r="I106" t="inlineStr">
-        <is>
-          <t>待機中</t>
-        </is>
-      </c>
-      <c r="J106" t="n">
-        <v>5</v>
-      </c>
     </row>
     <row r="107">
       <c r="A107" t="n">
@@ -6491,17 +5321,6 @@
           <t>【種別：指定避難所】【対応災害：洪水】【所在地：大分県日田市大山町西大山2042-9】</t>
         </is>
       </c>
-      <c r="H107" t="n">
-        <v>0</v>
-      </c>
-      <c r="I107" t="inlineStr">
-        <is>
-          <t>待機中</t>
-        </is>
-      </c>
-      <c r="J107" t="n">
-        <v>5</v>
-      </c>
     </row>
     <row r="108">
       <c r="A108" t="n">
@@ -6533,17 +5352,6 @@
           <t>【種別：指定避難所】【対応災害：洪水, 崖崩れ・土石流, 地震】【所在地：大分県日田市大山町西大山870-5】</t>
         </is>
       </c>
-      <c r="H108" t="n">
-        <v>0</v>
-      </c>
-      <c r="I108" t="inlineStr">
-        <is>
-          <t>待機中</t>
-        </is>
-      </c>
-      <c r="J108" t="n">
-        <v>5</v>
-      </c>
     </row>
     <row r="109">
       <c r="A109" t="n">
@@ -6575,17 +5383,6 @@
           <t>【種別：指定避難所】【対応災害：洪水, 崖崩れ・土石流, 地震】【所在地：大分県日田市大山町東大山1157】</t>
         </is>
       </c>
-      <c r="H109" t="n">
-        <v>0</v>
-      </c>
-      <c r="I109" t="inlineStr">
-        <is>
-          <t>待機中</t>
-        </is>
-      </c>
-      <c r="J109" t="n">
-        <v>5</v>
-      </c>
     </row>
     <row r="110">
       <c r="A110" t="n">
@@ -6617,17 +5414,6 @@
           <t>【種別：指定避難所】【対応災害：洪水, 崖崩れ・土石流, 地震】【所在地：大分県日田市大山町東大山470-3】</t>
         </is>
       </c>
-      <c r="H110" t="n">
-        <v>0</v>
-      </c>
-      <c r="I110" t="inlineStr">
-        <is>
-          <t>待機中</t>
-        </is>
-      </c>
-      <c r="J110" t="n">
-        <v>5</v>
-      </c>
     </row>
     <row r="111">
       <c r="A111" t="n">
@@ -6659,17 +5445,6 @@
           <t>【種別：指定避難所】【対応災害：洪水】【所在地：大分県日田市大山町西大山3600】【連絡先：(0973)52-3101】</t>
         </is>
       </c>
-      <c r="H111" t="n">
-        <v>0</v>
-      </c>
-      <c r="I111" t="inlineStr">
-        <is>
-          <t>待機中</t>
-        </is>
-      </c>
-      <c r="J111" t="n">
-        <v>5</v>
-      </c>
     </row>
     <row r="112">
       <c r="A112" t="n">
@@ -6701,17 +5476,6 @@
           <t>【種別：指定避難所】【対応災害：地震】【所在地：大分県日田市大山町西大山3615-1】【連絡先：(0973)52-2051】</t>
         </is>
       </c>
-      <c r="H112" t="n">
-        <v>0</v>
-      </c>
-      <c r="I112" t="inlineStr">
-        <is>
-          <t>待機中</t>
-        </is>
-      </c>
-      <c r="J112" t="n">
-        <v>5</v>
-      </c>
     </row>
     <row r="113">
       <c r="A113" t="n">
@@ -6743,17 +5507,6 @@
           <t>【種別：指定避難所】【対応災害：洪水, 崖崩れ・土石流, 地震】【所在地：大分県日田市天瀬町女子畑1298-1】【連絡先：(0973)57-3031】</t>
         </is>
       </c>
-      <c r="H113" t="n">
-        <v>0</v>
-      </c>
-      <c r="I113" t="inlineStr">
-        <is>
-          <t>待機中</t>
-        </is>
-      </c>
-      <c r="J113" t="n">
-        <v>5</v>
-      </c>
     </row>
     <row r="114">
       <c r="A114" t="n">
@@ -6785,17 +5538,6 @@
           <t>【種別：指定避難所】【対応災害：洪水】【所在地：大分県日田市天瀬町合田747-1】【連絡先：(0973)57-2507】</t>
         </is>
       </c>
-      <c r="H114" t="n">
-        <v>0</v>
-      </c>
-      <c r="I114" t="inlineStr">
-        <is>
-          <t>待機中</t>
-        </is>
-      </c>
-      <c r="J114" t="n">
-        <v>5</v>
-      </c>
     </row>
     <row r="115">
       <c r="A115" t="n">
@@ -6827,17 +5569,6 @@
           <t>【種別：指定避難所】【対応災害：洪水, 崖崩れ・土石流, 地震】【所在地：大分県日田市天瀬町桜竹244-1】【連絡先：(0973)57-3030】</t>
         </is>
       </c>
-      <c r="H115" t="n">
-        <v>0</v>
-      </c>
-      <c r="I115" t="inlineStr">
-        <is>
-          <t>待機中</t>
-        </is>
-      </c>
-      <c r="J115" t="n">
-        <v>5</v>
-      </c>
     </row>
     <row r="116">
       <c r="A116" t="n">
@@ -6869,17 +5600,6 @@
           <t>【種別：指定避難所】【対応災害：洪水, 崖崩れ・土石流, 地震】【所在地：大分県日田市天瀬町出口1840-1】【連絡先：(0973)57-2762】</t>
         </is>
       </c>
-      <c r="H116" t="n">
-        <v>0</v>
-      </c>
-      <c r="I116" t="inlineStr">
-        <is>
-          <t>待機中</t>
-        </is>
-      </c>
-      <c r="J116" t="n">
-        <v>5</v>
-      </c>
     </row>
     <row r="117">
       <c r="A117" t="n">
@@ -6911,17 +5631,6 @@
           <t>【種別：指定避難所】【対応災害：洪水, 崖崩れ・土石流, 地震】【所在地：大分県日田市天瀬町五馬市2054-1】【連絡先：(0973)57-2750】</t>
         </is>
       </c>
-      <c r="H117" t="n">
-        <v>0</v>
-      </c>
-      <c r="I117" t="inlineStr">
-        <is>
-          <t>待機中</t>
-        </is>
-      </c>
-      <c r="J117" t="n">
-        <v>5</v>
-      </c>
     </row>
     <row r="118">
       <c r="A118" t="n">
@@ -6953,17 +5662,6 @@
           <t>【種別：指定避難所】【対応災害：崖崩れ・土石流, 地震】【所在地：大分県日田市天瀬町馬原2276-1】【連絡先：(0973)57-2506】</t>
         </is>
       </c>
-      <c r="H118" t="n">
-        <v>0</v>
-      </c>
-      <c r="I118" t="inlineStr">
-        <is>
-          <t>待機中</t>
-        </is>
-      </c>
-      <c r="J118" t="n">
-        <v>5</v>
-      </c>
     </row>
     <row r="119">
       <c r="A119" t="n">
@@ -6995,17 +5693,6 @@
           <t>【種別：指定避難所】【対応災害：洪水, 崖崩れ・土石流, 地震】【所在地：大分県日田市天瀬町塚田169-2】【連絡先：(0973)57-2036】</t>
         </is>
       </c>
-      <c r="H119" t="n">
-        <v>0</v>
-      </c>
-      <c r="I119" t="inlineStr">
-        <is>
-          <t>待機中</t>
-        </is>
-      </c>
-      <c r="J119" t="n">
-        <v>5</v>
-      </c>
     </row>
     <row r="120">
       <c r="A120" t="n">
@@ -7037,17 +5724,6 @@
           <t>【種別：指定避難所】【対応災害：地震】【所在地：大分県日田市天瀬町合田1986-2】【連絡先：(0973)57-3157】</t>
         </is>
       </c>
-      <c r="H120" t="n">
-        <v>0</v>
-      </c>
-      <c r="I120" t="inlineStr">
-        <is>
-          <t>待機中</t>
-        </is>
-      </c>
-      <c r="J120" t="n">
-        <v>5</v>
-      </c>
     </row>
     <row r="121">
       <c r="A121" t="n">
@@ -7079,17 +5755,6 @@
           <t>【種別：指定避難所】【対応災害：崖崩れ・土石流, 地震】【所在地：大分県日田市天瀬町桜竹671-2】【連絡先：(0973)57-8212】</t>
         </is>
       </c>
-      <c r="H121" t="n">
-        <v>0</v>
-      </c>
-      <c r="I121" t="inlineStr">
-        <is>
-          <t>待機中</t>
-        </is>
-      </c>
-      <c r="J121" t="n">
-        <v>5</v>
-      </c>
     </row>
     <row r="122">
       <c r="A122" t="n">
@@ -7121,17 +5786,6 @@
           <t>【種別：指定避難所】【対応災害：洪水, 崖崩れ・土石流, 地震】【所在地：大分県日田市天瀬町桜竹80-1】【連絡先：(0973)57-3999】</t>
         </is>
       </c>
-      <c r="H122" t="n">
-        <v>0</v>
-      </c>
-      <c r="I122" t="inlineStr">
-        <is>
-          <t>待機中</t>
-        </is>
-      </c>
-      <c r="J122" t="n">
-        <v>5</v>
-      </c>
     </row>
     <row r="123">
       <c r="A123" t="n">
@@ -7162,17 +5816,6 @@
         <is>
           <t>【種別：指定避難所】【対応災害：洪水, 崖崩れ・土石流, 地震】【所在地：大分県日田市天瀬町五馬市2166-1】【連絡先：(0973)57-2994】</t>
         </is>
-      </c>
-      <c r="H123" t="n">
-        <v>0</v>
-      </c>
-      <c r="I123" t="inlineStr">
-        <is>
-          <t>待機中</t>
-        </is>
-      </c>
-      <c r="J123" t="n">
-        <v>5</v>
       </c>
     </row>
   </sheetData>

--- a/spots_en.xlsx
+++ b/spots_en.xlsx
@@ -3747,7 +3747,7 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>大分県立日田林工高等学校</t>
+          <t>大分県立日田林工高等学校（体育館）</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
@@ -3768,7 +3768,7 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>【種別：指定避難所】【対応災害：崖崩れ・土石流, 地震】【所在地：大分県日田市吹上町30】【連絡先：(0973)22-5171】</t>
+          <t>【種別：指定避難所】【避難場所：体育館】【対応災害：崖崩れ・土石流, 地震】【所在地：大分県日田市吹上町30】【連絡先：(0973)22-5171】</t>
         </is>
       </c>
     </row>

--- a/spots_en.xlsx
+++ b/spots_en.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G50"/>
+  <dimension ref="A1:Q50"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -465,6 +465,56 @@
           <t>説明</t>
         </is>
       </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>景観度</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>落ち着ける度</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>賑やか度</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>子供向け度</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>インスタ映え度</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>歴史・文化度</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>アクセス度</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>非日常度</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>体験度</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
+          <t>コスパ度</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -496,6 +546,16 @@
           <t>【歴史】江戸時代の町並みが残る風情ある商家町。2月には「おひなまつり」、11月には「千年あかり」が開催され、幻想的な灯りに包まれます。</t>
         </is>
       </c>
+      <c r="H2" t="inlineStr"/>
+      <c r="I2" t="inlineStr"/>
+      <c r="J2" t="inlineStr"/>
+      <c r="K2" t="inlineStr"/>
+      <c r="L2" t="inlineStr"/>
+      <c r="M2" t="inlineStr"/>
+      <c r="N2" t="inlineStr"/>
+      <c r="O2" t="inlineStr"/>
+      <c r="P2" t="inlineStr"/>
+      <c r="Q2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -527,6 +587,16 @@
           <t>江戸時代後期に廣瀬淡窓が開いた日本最大規模の私塾跡。世界遺産構成資産。咸宜園教育研究センターで歴史を学べる。身分や出身地を問わない画期的な教育施設。住所：日田市淡窓2丁目2-13</t>
         </is>
       </c>
+      <c r="H3" t="inlineStr"/>
+      <c r="I3" t="inlineStr"/>
+      <c r="J3" t="inlineStr"/>
+      <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr"/>
+      <c r="M3" t="inlineStr"/>
+      <c r="N3" t="inlineStr"/>
+      <c r="O3" t="inlineStr"/>
+      <c r="P3" t="inlineStr"/>
+      <c r="Q3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -558,6 +628,16 @@
           <t>【アンケート人気：14件】「静かで勉強しやすい」「涼しい」と学生に人気。Wi-Fi完備で学習スペースも充実。咸宜園の歴史展示も併設。住所：日田市上城内町1-72</t>
         </is>
       </c>
+      <c r="H4" t="inlineStr"/>
+      <c r="I4" t="inlineStr"/>
+      <c r="J4" t="inlineStr"/>
+      <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr"/>
+      <c r="N4" t="inlineStr"/>
+      <c r="O4" t="inlineStr"/>
+      <c r="P4" t="inlineStr"/>
+      <c r="Q4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -589,6 +669,16 @@
           <t>AOSE内3階にある博物館。地域の歴史や文化を学べる。天領時代の資料、考古資料、民俗資料を展示。季節ごとに展示内容が変わる。住所：日田市上城内町2-6（AOSE内3階）</t>
         </is>
       </c>
+      <c r="H5" t="inlineStr"/>
+      <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr"/>
+      <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
+      <c r="M5" t="inlineStr"/>
+      <c r="N5" t="inlineStr"/>
+      <c r="O5" t="inlineStr"/>
+      <c r="P5" t="inlineStr"/>
+      <c r="Q5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -620,6 +710,16 @@
           <t>【文化】ユネスコ無形文化遺産の「日田祇園祭」で使われる豪華な山鉾を展示。7月の祭り本番では街中を圧巻の山鉾が練り歩きます。</t>
         </is>
       </c>
+      <c r="H6" t="inlineStr"/>
+      <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr"/>
+      <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
+      <c r="M6" t="inlineStr"/>
+      <c r="N6" t="inlineStr"/>
+      <c r="O6" t="inlineStr"/>
+      <c r="P6" t="inlineStr"/>
+      <c r="Q6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -651,6 +751,16 @@
           <t>【アンケート人気：2件】豆田町にある資料館。天領時代の日田の歴史や文化を展示。毎年2〜3月には「天領日田おひなまつり」開催。江戸〜昭和のひな人形コレクション。住所：日田市豆田町11-7</t>
         </is>
       </c>
+      <c r="H7" t="inlineStr"/>
+      <c r="I7" t="inlineStr"/>
+      <c r="J7" t="inlineStr"/>
+      <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
+      <c r="M7" t="inlineStr"/>
+      <c r="N7" t="inlineStr"/>
+      <c r="O7" t="inlineStr"/>
+      <c r="P7" t="inlineStr"/>
+      <c r="Q7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -682,6 +792,16 @@
           <t>【アンケート人気：14件】三隈川沿いの桜の名所。「遊具がいっぱい」「自然豊か」と人気。約1,000本の桜。展望台から日田市街地を一望。遊具、ウォーキングコース完備。住所：日田市中ノ島町559番地</t>
         </is>
       </c>
+      <c r="H8" t="inlineStr"/>
+      <c r="I8" t="inlineStr"/>
+      <c r="J8" t="inlineStr"/>
+      <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
+      <c r="M8" t="inlineStr"/>
+      <c r="N8" t="inlineStr"/>
+      <c r="O8" t="inlineStr"/>
+      <c r="P8" t="inlineStr"/>
+      <c r="Q8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -713,6 +833,16 @@
           <t>【水郷】日田を象徴する美しい川。5月の「川開き観光祭」では大花火大会が開催され、屋形船での鵜飼い体験も楽しめます。</t>
         </is>
       </c>
+      <c r="H9" t="inlineStr"/>
+      <c r="I9" t="inlineStr"/>
+      <c r="J9" t="inlineStr"/>
+      <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr"/>
+      <c r="M9" t="inlineStr"/>
+      <c r="N9" t="inlineStr"/>
+      <c r="O9" t="inlineStr"/>
+      <c r="P9" t="inlineStr"/>
+      <c r="Q9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -744,6 +874,16 @@
           <t>三隈川沿いの遊歩道。川のほとりを歩きながら自然の美しさを感じられる。対岸の景色が水面に映り込み、夕暮れ時や夜間は特に美しい。ジョギングや散歩に最適。住所：日田市隈２丁目３-8</t>
         </is>
       </c>
+      <c r="H10" t="inlineStr"/>
+      <c r="I10" t="inlineStr"/>
+      <c r="J10" t="inlineStr"/>
+      <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr"/>
+      <c r="M10" t="inlineStr"/>
+      <c r="N10" t="inlineStr"/>
+      <c r="O10" t="inlineStr"/>
+      <c r="P10" t="inlineStr"/>
+      <c r="Q10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -775,6 +915,16 @@
           <t>【アンケート人気：4件】市街地中心部の高台にある公園。見晴らし良好。「落ち着く」と地元住民に愛される憩いの場。緊急避難場所にも指定。住所：日田市丸山2丁目2-1</t>
         </is>
       </c>
+      <c r="H11" t="inlineStr"/>
+      <c r="I11" t="inlineStr"/>
+      <c r="J11" t="inlineStr"/>
+      <c r="K11" t="inlineStr"/>
+      <c r="L11" t="inlineStr"/>
+      <c r="M11" t="inlineStr"/>
+      <c r="N11" t="inlineStr"/>
+      <c r="O11" t="inlineStr"/>
+      <c r="P11" t="inlineStr"/>
+      <c r="Q11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -806,6 +956,16 @@
           <t>上段20m、下段10mの二段滝。滝の裏側から眺められる「裏見の滝」として有名。夜間はライトアップ。道の駅「慈恩の滝くす」隣接。住所：玖珠郡玖珠町山浦618</t>
         </is>
       </c>
+      <c r="H12" t="inlineStr"/>
+      <c r="I12" t="inlineStr"/>
+      <c r="J12" t="inlineStr"/>
+      <c r="K12" t="inlineStr"/>
+      <c r="L12" t="inlineStr"/>
+      <c r="M12" t="inlineStr"/>
+      <c r="N12" t="inlineStr"/>
+      <c r="O12" t="inlineStr"/>
+      <c r="P12" t="inlineStr"/>
+      <c r="Q12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -837,6 +997,16 @@
           <t>落差約25m、幅約15mの滝。水が飛散する様子が桜の花びらに似ている。周辺に桜が植えられ、春は桜と滝のコラボレーション。遊歩道整備。住所：日田市天瀬町桜竹</t>
         </is>
       </c>
+      <c r="H13" t="inlineStr"/>
+      <c r="I13" t="inlineStr"/>
+      <c r="J13" t="inlineStr"/>
+      <c r="K13" t="inlineStr"/>
+      <c r="L13" t="inlineStr"/>
+      <c r="M13" t="inlineStr"/>
+      <c r="N13" t="inlineStr"/>
+      <c r="O13" t="inlineStr"/>
+      <c r="P13" t="inlineStr"/>
+      <c r="Q13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -868,6 +1038,16 @@
           <t>【絶景】進撃の巨人の作者・諫山創先生の故郷。エレン・ミカサ・アルミンの銅像がダムを見上げる姿はファン必見のスポットです。</t>
         </is>
       </c>
+      <c r="H14" t="inlineStr"/>
+      <c r="I14" t="inlineStr"/>
+      <c r="J14" t="inlineStr"/>
+      <c r="K14" t="inlineStr"/>
+      <c r="L14" t="inlineStr"/>
+      <c r="M14" t="inlineStr"/>
+      <c r="N14" t="inlineStr"/>
+      <c r="O14" t="inlineStr"/>
+      <c r="P14" t="inlineStr"/>
+      <c r="Q14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -899,6 +1079,16 @@
           <t>【アンケート人気：2件】標高約760mの山。登山コース整備。山頂から日田市街地や九重連山を一望。春は山桜、秋は紅葉。トレッキング愛好者に人気。住所：日田市小野</t>
         </is>
       </c>
+      <c r="H15" t="inlineStr"/>
+      <c r="I15" t="inlineStr"/>
+      <c r="J15" t="inlineStr"/>
+      <c r="K15" t="inlineStr"/>
+      <c r="L15" t="inlineStr"/>
+      <c r="M15" t="inlineStr"/>
+      <c r="N15" t="inlineStr"/>
+      <c r="O15" t="inlineStr"/>
+      <c r="P15" t="inlineStr"/>
+      <c r="Q15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -930,6 +1120,16 @@
           <t>大山町の梅園。日田市内を一望できる絶景スポット。360度パノラマビュー。夕日や夜景が特に美しい。春には梅が咲き誇る。住所：日田市大山町西大山４７３８</t>
         </is>
       </c>
+      <c r="H16" t="inlineStr"/>
+      <c r="I16" t="inlineStr"/>
+      <c r="J16" t="inlineStr"/>
+      <c r="K16" t="inlineStr"/>
+      <c r="L16" t="inlineStr"/>
+      <c r="M16" t="inlineStr"/>
+      <c r="N16" t="inlineStr"/>
+      <c r="O16" t="inlineStr"/>
+      <c r="P16" t="inlineStr"/>
+      <c r="Q16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -961,6 +1161,16 @@
           <t>標高700mの高原。360度パノラマビューで展望抜群。夏はひまわり、秋はコスモスが咲く。ドライブスポットとして人気。住所：日田市天瀬町</t>
         </is>
       </c>
+      <c r="H17" t="inlineStr"/>
+      <c r="I17" t="inlineStr"/>
+      <c r="J17" t="inlineStr"/>
+      <c r="K17" t="inlineStr"/>
+      <c r="L17" t="inlineStr"/>
+      <c r="M17" t="inlineStr"/>
+      <c r="N17" t="inlineStr"/>
+      <c r="O17" t="inlineStr"/>
+      <c r="P17" t="inlineStr"/>
+      <c r="Q17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -992,6 +1202,16 @@
           <t>古墳群が保存されている公園。歴史を感じながら散策できる。遊具もあり、子供の遊び場としても人気。広い芝生広場でピクニック可能。住所：日田市石井３丁目1184-1</t>
         </is>
       </c>
+      <c r="H18" t="inlineStr"/>
+      <c r="I18" t="inlineStr"/>
+      <c r="J18" t="inlineStr"/>
+      <c r="K18" t="inlineStr"/>
+      <c r="L18" t="inlineStr"/>
+      <c r="M18" t="inlineStr"/>
+      <c r="N18" t="inlineStr"/>
+      <c r="O18" t="inlineStr"/>
+      <c r="P18" t="inlineStr"/>
+      <c r="Q18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -1023,6 +1243,16 @@
           <t>三隈川と花月川の合流点にある星隈の丘の公園。古墳群が点在し、歴史的価値が高い。眺望良好で静かな散策が楽しめる穴場スポット。住所：日田市友田２丁目</t>
         </is>
       </c>
+      <c r="H19" t="inlineStr"/>
+      <c r="I19" t="inlineStr"/>
+      <c r="J19" t="inlineStr"/>
+      <c r="K19" t="inlineStr"/>
+      <c r="L19" t="inlineStr"/>
+      <c r="M19" t="inlineStr"/>
+      <c r="N19" t="inlineStr"/>
+      <c r="O19" t="inlineStr"/>
+      <c r="P19" t="inlineStr"/>
+      <c r="Q19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -1054,6 +1284,16 @@
           <t>市南部の丘陵地にある公園。多くの桜が植えられ、春には桜の絨毯ができる。散策路沿いに美しい桜並木。地元住民の花見スポット。住所：日田市上野147-1</t>
         </is>
       </c>
+      <c r="H20" t="inlineStr"/>
+      <c r="I20" t="inlineStr"/>
+      <c r="J20" t="inlineStr"/>
+      <c r="K20" t="inlineStr"/>
+      <c r="L20" t="inlineStr"/>
+      <c r="M20" t="inlineStr"/>
+      <c r="N20" t="inlineStr"/>
+      <c r="O20" t="inlineStr"/>
+      <c r="P20" t="inlineStr"/>
+      <c r="Q20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -1085,6 +1325,16 @@
           <t>【アンケート人気：2件】約1,300年の歴史を持つ温泉地。豊後三大温泉の一つ。玖珠川沿いに温泉旅館が並び、共同露天風呂も点在。秋の紅葉シーズンは特に美しい。住所：日田市天瀬町湯山</t>
         </is>
       </c>
+      <c r="H21" t="inlineStr"/>
+      <c r="I21" t="inlineStr"/>
+      <c r="J21" t="inlineStr"/>
+      <c r="K21" t="inlineStr"/>
+      <c r="L21" t="inlineStr"/>
+      <c r="M21" t="inlineStr"/>
+      <c r="N21" t="inlineStr"/>
+      <c r="O21" t="inlineStr"/>
+      <c r="P21" t="inlineStr"/>
+      <c r="Q21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -1116,6 +1366,16 @@
           <t>【アンケート人気：4件】天ヶ瀬温泉街の日帰り温泉施設。地元住民にも愛される。露天風呂からの景色が良くリラックスできる。料金も手頃で気軽に温泉を楽しめる。住所：〒877-0032 大分県日田市小ケ瀬町２７５０</t>
         </is>
       </c>
+      <c r="H22" t="inlineStr"/>
+      <c r="I22" t="inlineStr"/>
+      <c r="J22" t="inlineStr"/>
+      <c r="K22" t="inlineStr"/>
+      <c r="L22" t="inlineStr"/>
+      <c r="M22" t="inlineStr"/>
+      <c r="N22" t="inlineStr"/>
+      <c r="O22" t="inlineStr"/>
+      <c r="P22" t="inlineStr"/>
+      <c r="Q22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -1147,6 +1407,16 @@
           <t>【アンケート人気：4件】「3時間1000円パックで温泉・サウナ・足湯、漫画やネトフリも楽しめる」と人気。天ヶ瀬温泉街のリラックススペース。コスパ抜群の施設。住所：〒877-0044 大分県日田市隈１丁目３−８</t>
         </is>
       </c>
+      <c r="H23" t="inlineStr"/>
+      <c r="I23" t="inlineStr"/>
+      <c r="J23" t="inlineStr"/>
+      <c r="K23" t="inlineStr"/>
+      <c r="L23" t="inlineStr"/>
+      <c r="M23" t="inlineStr"/>
+      <c r="N23" t="inlineStr"/>
+      <c r="O23" t="inlineStr"/>
+      <c r="P23" t="inlineStr"/>
+      <c r="Q23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -1178,6 +1448,16 @@
           <t>【アンケート人気：5件】日田市最大の八幡宮。「景色が綺麗」「落ち着く」「雰囲気が好き」と評価。立派な本殿と境内。日田祇園祭で重要な役割。市街地から徒歩圏内。住所：〒877-0023 大分県日田市田島２丁目１８４</t>
         </is>
       </c>
+      <c r="H24" t="inlineStr"/>
+      <c r="I24" t="inlineStr"/>
+      <c r="J24" t="inlineStr"/>
+      <c r="K24" t="inlineStr"/>
+      <c r="L24" t="inlineStr"/>
+      <c r="M24" t="inlineStr"/>
+      <c r="N24" t="inlineStr"/>
+      <c r="O24" t="inlineStr"/>
+      <c r="P24" t="inlineStr"/>
+      <c r="Q24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -1209,6 +1489,16 @@
           <t>天瀬町の地蔵尊。あらゆる願い事を叶えるパワースポットとして全国から参拝者が訪れる。境内に数多くの地蔵が並ぶ。神仏習合の珍しい形態。住所：〒879-4121 大分県日田市天瀬町馬原３７４０</t>
         </is>
       </c>
+      <c r="H25" t="inlineStr"/>
+      <c r="I25" t="inlineStr"/>
+      <c r="J25" t="inlineStr"/>
+      <c r="K25" t="inlineStr"/>
+      <c r="L25" t="inlineStr"/>
+      <c r="M25" t="inlineStr"/>
+      <c r="N25" t="inlineStr"/>
+      <c r="O25" t="inlineStr"/>
+      <c r="P25" t="inlineStr"/>
+      <c r="Q25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -1240,6 +1530,16 @@
           <t>市内中心部の高台にあり、石段を登った先に社殿。眺望良く、日田市街地を見渡せる。金刀比羅宮を勧請。海上安全や商売繁盛の神として信仰。住所：〒838-1701 福岡県朝倉郡東峰村宝珠山</t>
         </is>
       </c>
+      <c r="H26" t="inlineStr"/>
+      <c r="I26" t="inlineStr"/>
+      <c r="J26" t="inlineStr"/>
+      <c r="K26" t="inlineStr"/>
+      <c r="L26" t="inlineStr"/>
+      <c r="M26" t="inlineStr"/>
+      <c r="N26" t="inlineStr"/>
+      <c r="O26" t="inlineStr"/>
+      <c r="P26" t="inlineStr"/>
+      <c r="Q26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -1271,6 +1571,16 @@
           <t>1014年に日田領主・大蔵永弘が創建した浄土宗の寺院。自現山公園入口に位置。日田駅から北へ約1.5km、花月川に架かる城町橋近く。歴史ある寺院。住所：〒877-0004 大分県日田市城町２丁目５−３</t>
         </is>
       </c>
+      <c r="H27" t="inlineStr"/>
+      <c r="I27" t="inlineStr"/>
+      <c r="J27" t="inlineStr"/>
+      <c r="K27" t="inlineStr"/>
+      <c r="L27" t="inlineStr"/>
+      <c r="M27" t="inlineStr"/>
+      <c r="N27" t="inlineStr"/>
+      <c r="O27" t="inlineStr"/>
+      <c r="P27" t="inlineStr"/>
+      <c r="Q27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -1302,6 +1612,16 @@
           <t>1338年創建の古刹。九州最古の庭園（約500㎡）を持つ。参道沿いの庭園が見どころ。静かで落ち着いた雰囲気。住所：〒877-0301 大分県日田市中津江村栃野４７２</t>
         </is>
       </c>
+      <c r="H28" t="inlineStr"/>
+      <c r="I28" t="inlineStr"/>
+      <c r="J28" t="inlineStr"/>
+      <c r="K28" t="inlineStr"/>
+      <c r="L28" t="inlineStr"/>
+      <c r="M28" t="inlineStr"/>
+      <c r="N28" t="inlineStr"/>
+      <c r="O28" t="inlineStr"/>
+      <c r="P28" t="inlineStr"/>
+      <c r="Q28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -1333,6 +1653,16 @@
           <t>1702年創建。毎年10月28日に大祭が行われる。自然の山間に静かに佇む霊場。地元の信仰を集める。住所：日田市天瀬町馬原</t>
         </is>
       </c>
+      <c r="H29" t="inlineStr"/>
+      <c r="I29" t="inlineStr"/>
+      <c r="J29" t="inlineStr"/>
+      <c r="K29" t="inlineStr"/>
+      <c r="L29" t="inlineStr"/>
+      <c r="M29" t="inlineStr"/>
+      <c r="N29" t="inlineStr"/>
+      <c r="O29" t="inlineStr"/>
+      <c r="P29" t="inlineStr"/>
+      <c r="Q29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -1364,6 +1694,16 @@
           <t>起源は680年（天武天皇9年）にさかのぼる古社。天瀬町鞍形尾の岩松ヶ峰に八幡宮を祀ったのが始まり。歴史的価値の高い神社。住所：日田市天瀬町馬原５００</t>
         </is>
       </c>
+      <c r="H30" t="inlineStr"/>
+      <c r="I30" t="inlineStr"/>
+      <c r="J30" t="inlineStr"/>
+      <c r="K30" t="inlineStr"/>
+      <c r="L30" t="inlineStr"/>
+      <c r="M30" t="inlineStr"/>
+      <c r="N30" t="inlineStr"/>
+      <c r="O30" t="inlineStr"/>
+      <c r="P30" t="inlineStr"/>
+      <c r="Q30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -1395,6 +1735,16 @@
           <t>烏宿山（標高550m）の山頂に建つ神社。1,000年以上の歴史。かつて女人禁制の修験の霊山だった。登山を兼ねた参拝が可能。眺望抜群。住所：日田市大山町西大山</t>
         </is>
       </c>
+      <c r="H31" t="inlineStr"/>
+      <c r="I31" t="inlineStr"/>
+      <c r="J31" t="inlineStr"/>
+      <c r="K31" t="inlineStr"/>
+      <c r="L31" t="inlineStr"/>
+      <c r="M31" t="inlineStr"/>
+      <c r="N31" t="inlineStr"/>
+      <c r="O31" t="inlineStr"/>
+      <c r="P31" t="inlineStr"/>
+      <c r="Q31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -1426,6 +1776,16 @@
           <t>約300年の伝統を持つ民陶の里。10軒の窯元が伝統技法を守り継承。一子相伝の完全世襲制。作陶見学や器の購入が可能。国の重要無形文化財。住所：日田市小野２３４</t>
         </is>
       </c>
+      <c r="H32" t="inlineStr"/>
+      <c r="I32" t="inlineStr"/>
+      <c r="J32" t="inlineStr"/>
+      <c r="K32" t="inlineStr"/>
+      <c r="L32" t="inlineStr"/>
+      <c r="M32" t="inlineStr"/>
+      <c r="N32" t="inlineStr"/>
+      <c r="O32" t="inlineStr"/>
+      <c r="P32" t="inlineStr"/>
+      <c r="Q32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -1457,6 +1817,16 @@
           <t>ビール製造工程を見学できる工場（要予約）。試飲コーナーで出来たてのビールを楽しめる。日田の良質な水を使用。併設のレストランあり。無料で見学可能。住所：日田市高瀬６９７９</t>
         </is>
       </c>
+      <c r="H33" t="inlineStr"/>
+      <c r="I33" t="inlineStr"/>
+      <c r="J33" t="inlineStr"/>
+      <c r="K33" t="inlineStr"/>
+      <c r="L33" t="inlineStr"/>
+      <c r="M33" t="inlineStr"/>
+      <c r="N33" t="inlineStr"/>
+      <c r="O33" t="inlineStr"/>
+      <c r="P33" t="inlineStr"/>
+      <c r="Q33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -1488,6 +1858,16 @@
           <t>江戸時代から昭和まで稼働していた金山跡。坑道内部を見学でき、採掘の歴史を学べる。砂金採り体験も可能。中津江村の観光スポット。住所：日田市中津江村合瀬3750</t>
         </is>
       </c>
+      <c r="H34" t="inlineStr"/>
+      <c r="I34" t="inlineStr"/>
+      <c r="J34" t="inlineStr"/>
+      <c r="K34" t="inlineStr"/>
+      <c r="L34" t="inlineStr"/>
+      <c r="M34" t="inlineStr"/>
+      <c r="N34" t="inlineStr"/>
+      <c r="O34" t="inlineStr"/>
+      <c r="P34" t="inlineStr"/>
+      <c r="Q34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -1519,6 +1899,16 @@
           <t>日田の名水「天領水」の湧水を利用。直販市、レストラン、土産物店、足湯を備える。無料で水を汲める。地元の新鮮な農産物や特産品が並ぶ。住所：日田市庄手６３５−１</t>
         </is>
       </c>
+      <c r="H35" t="inlineStr"/>
+      <c r="I35" t="inlineStr"/>
+      <c r="J35" t="inlineStr"/>
+      <c r="K35" t="inlineStr"/>
+      <c r="L35" t="inlineStr"/>
+      <c r="M35" t="inlineStr"/>
+      <c r="N35" t="inlineStr"/>
+      <c r="O35" t="inlineStr"/>
+      <c r="P35" t="inlineStr"/>
+      <c r="Q35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="n">
@@ -1550,6 +1940,16 @@
           <t>大山地区の道の駅。地元農産物の直売所、レストラン、休憩所。大山ダムへのアクセス拠点。進撃の巨人関連グッズも販売。住所：日田市大山町西大山４１０６</t>
         </is>
       </c>
+      <c r="H36" t="inlineStr"/>
+      <c r="I36" t="inlineStr"/>
+      <c r="J36" t="inlineStr"/>
+      <c r="K36" t="inlineStr"/>
+      <c r="L36" t="inlineStr"/>
+      <c r="M36" t="inlineStr"/>
+      <c r="N36" t="inlineStr"/>
+      <c r="O36" t="inlineStr"/>
+      <c r="P36" t="inlineStr"/>
+      <c r="Q36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="n">
@@ -1581,6 +1981,16 @@
           <t>中津江地区の道の駅。鯛生金山と併設。地元特産品の販売、レストラン。山間部の休憩スポット。住所：日田市中津江村合瀬３７５０</t>
         </is>
       </c>
+      <c r="H37" t="inlineStr"/>
+      <c r="I37" t="inlineStr"/>
+      <c r="J37" t="inlineStr"/>
+      <c r="K37" t="inlineStr"/>
+      <c r="L37" t="inlineStr"/>
+      <c r="M37" t="inlineStr"/>
+      <c r="N37" t="inlineStr"/>
+      <c r="O37" t="inlineStr"/>
+      <c r="P37" t="inlineStr"/>
+      <c r="Q37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="n">
@@ -1612,6 +2022,16 @@
           <t>川の水を利用した屋外プール（夏季限定）。透明度が高く冷たい水。家族向けの遊具もあり、子供連れに人気。更衣室、休憩所完備。住所：日田市小野４８３０−３</t>
         </is>
       </c>
+      <c r="H38" t="inlineStr"/>
+      <c r="I38" t="inlineStr"/>
+      <c r="J38" t="inlineStr"/>
+      <c r="K38" t="inlineStr"/>
+      <c r="L38" t="inlineStr"/>
+      <c r="M38" t="inlineStr"/>
+      <c r="N38" t="inlineStr"/>
+      <c r="O38" t="inlineStr"/>
+      <c r="P38" t="inlineStr"/>
+      <c r="Q38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="n">
@@ -1643,6 +2063,16 @@
           <t>奥日田の美しい自然の渓谷を利用した本格的な渓流釣り。ニジマスなど。ログハウスでのキャンプも可能。夏は90mウォータースライダーも。営業：9:00-17:00、水曜休。住所：日田市上津江町川原１６５６−９２</t>
         </is>
       </c>
+      <c r="H39" t="inlineStr"/>
+      <c r="I39" t="inlineStr"/>
+      <c r="J39" t="inlineStr"/>
+      <c r="K39" t="inlineStr"/>
+      <c r="L39" t="inlineStr"/>
+      <c r="M39" t="inlineStr"/>
+      <c r="N39" t="inlineStr"/>
+      <c r="O39" t="inlineStr"/>
+      <c r="P39" t="inlineStr"/>
+      <c r="Q39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="n">
@@ -1674,6 +2104,16 @@
           <t>標高950mのキャンプ場。晴天時は阿蘇五岳が見え、朝は雲海が広がる。スノーピーク直営ストア併設。本格的なキャンプを楽しめる。住所：日田市前津江町大野６４−１ 旧 椿ヶ鼻ハイランドパーク</t>
         </is>
       </c>
+      <c r="H40" t="inlineStr"/>
+      <c r="I40" t="inlineStr"/>
+      <c r="J40" t="inlineStr"/>
+      <c r="K40" t="inlineStr"/>
+      <c r="L40" t="inlineStr"/>
+      <c r="M40" t="inlineStr"/>
+      <c r="N40" t="inlineStr"/>
+      <c r="O40" t="inlineStr"/>
+      <c r="P40" t="inlineStr"/>
+      <c r="Q40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="n">
@@ -1705,6 +2145,16 @@
           <t>【アンケート人気：1件】「車やバイクが好きな人におすすめ」と評価される国際レーシングコース。スーパーGT等のビッグレース開催。サーキット走行体験も可能。住所：日田市上津江町上野田１１１２−８</t>
         </is>
       </c>
+      <c r="H41" t="inlineStr"/>
+      <c r="I41" t="inlineStr"/>
+      <c r="J41" t="inlineStr"/>
+      <c r="K41" t="inlineStr"/>
+      <c r="L41" t="inlineStr"/>
+      <c r="M41" t="inlineStr"/>
+      <c r="N41" t="inlineStr"/>
+      <c r="O41" t="inlineStr"/>
+      <c r="P41" t="inlineStr"/>
+      <c r="Q41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="n">
@@ -1736,6 +2186,16 @@
           <t>【アンケート人気：2件】「日田市内で唯一学生が楽しめる場所」と評価。ショッピング、飲食、娯楽が揃う複合商業施設。駐車場も広く、家族連れに人気。住所：日田市庄手６６１−１</t>
         </is>
       </c>
+      <c r="H42" t="inlineStr"/>
+      <c r="I42" t="inlineStr"/>
+      <c r="J42" t="inlineStr"/>
+      <c r="K42" t="inlineStr"/>
+      <c r="L42" t="inlineStr"/>
+      <c r="M42" t="inlineStr"/>
+      <c r="N42" t="inlineStr"/>
+      <c r="O42" t="inlineStr"/>
+      <c r="P42" t="inlineStr"/>
+      <c r="Q42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="n">
@@ -1767,6 +2227,16 @@
           <t>【アンケート人気：5件】「パフェ美味しい」「店がかわいい」と若者に人気のカフェ。おしゃれな内装とインスタ映えするスイーツ。地元食材を使った料理も評判。住所：日田市三本松１丁目１−２７</t>
         </is>
       </c>
+      <c r="H43" t="inlineStr"/>
+      <c r="I43" t="inlineStr"/>
+      <c r="J43" t="inlineStr"/>
+      <c r="K43" t="inlineStr"/>
+      <c r="L43" t="inlineStr"/>
+      <c r="M43" t="inlineStr"/>
+      <c r="N43" t="inlineStr"/>
+      <c r="O43" t="inlineStr"/>
+      <c r="P43" t="inlineStr"/>
+      <c r="Q43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="n">
@@ -1798,6 +2268,16 @@
           <t>【アンケート人気：5件】「夏には花火が見れる」「勉強できる」と人気。三隈川沿いに位置。Wi-Fi完備で学習スペースとしても利用される。住所：日田市庄手６４８−６</t>
         </is>
       </c>
+      <c r="H44" t="inlineStr"/>
+      <c r="I44" t="inlineStr"/>
+      <c r="J44" t="inlineStr"/>
+      <c r="K44" t="inlineStr"/>
+      <c r="L44" t="inlineStr"/>
+      <c r="M44" t="inlineStr"/>
+      <c r="N44" t="inlineStr"/>
+      <c r="O44" t="inlineStr"/>
+      <c r="P44" t="inlineStr"/>
+      <c r="Q44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="n">
@@ -1829,6 +2309,16 @@
           <t>【アンケート人気：3件】日田やきそばの元祖。鉄板で豪快に焼かれる焼きそばはもやしたっぷりでボリューム満点。創業以来変わらぬ味。豆田町散策の際の食事スポット。住所：日田市若宮町４１６−１</t>
         </is>
       </c>
+      <c r="H45" t="inlineStr"/>
+      <c r="I45" t="inlineStr"/>
+      <c r="J45" t="inlineStr"/>
+      <c r="K45" t="inlineStr"/>
+      <c r="L45" t="inlineStr"/>
+      <c r="M45" t="inlineStr"/>
+      <c r="N45" t="inlineStr"/>
+      <c r="O45" t="inlineStr"/>
+      <c r="P45" t="inlineStr"/>
+      <c r="Q45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="n">
@@ -1860,6 +2350,16 @@
           <t>【アンケート人気：2件】豆田町の人気飲食店。地元の食材を使った料理が評判。古民家を改装した雰囲気のある店内。観光客にも地元民にも人気。住所：日田市豆田町９−２</t>
         </is>
       </c>
+      <c r="H46" t="inlineStr"/>
+      <c r="I46" t="inlineStr"/>
+      <c r="J46" t="inlineStr"/>
+      <c r="K46" t="inlineStr"/>
+      <c r="L46" t="inlineStr"/>
+      <c r="M46" t="inlineStr"/>
+      <c r="N46" t="inlineStr"/>
+      <c r="O46" t="inlineStr"/>
+      <c r="P46" t="inlineStr"/>
+      <c r="Q46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="n">
@@ -1891,6 +2391,16 @@
           <t>日田インター近くのイタリアンレストラン。ふわふわのオムライスが人気。トマト、デミグラス、ハーフ&amp;ハーフから選べ、デザートとコーヒー付き。進撃の巨人コラボメニューも。住所：日田市丸山２丁目１−２６</t>
         </is>
       </c>
+      <c r="H47" t="inlineStr"/>
+      <c r="I47" t="inlineStr"/>
+      <c r="J47" t="inlineStr"/>
+      <c r="K47" t="inlineStr"/>
+      <c r="L47" t="inlineStr"/>
+      <c r="M47" t="inlineStr"/>
+      <c r="N47" t="inlineStr"/>
+      <c r="O47" t="inlineStr"/>
+      <c r="P47" t="inlineStr"/>
+      <c r="Q47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="n">
@@ -1922,6 +2432,16 @@
           <t>【アンケート人気：4件】市街地中心部の複合文化施設。「静かで周りにコンビニもあり、ミュージカルや演劇も多い」と評価。大ホール、会議室など多様なスペース。住所：日田市三本松１丁目８−１１</t>
         </is>
       </c>
+      <c r="H48" t="inlineStr"/>
+      <c r="I48" t="inlineStr"/>
+      <c r="J48" t="inlineStr"/>
+      <c r="K48" t="inlineStr"/>
+      <c r="L48" t="inlineStr"/>
+      <c r="M48" t="inlineStr"/>
+      <c r="N48" t="inlineStr"/>
+      <c r="O48" t="inlineStr"/>
+      <c r="P48" t="inlineStr"/>
+      <c r="Q48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="n">
@@ -1953,6 +2473,16 @@
           <t>【アンケート人気：4件】「勉強できる、Wi-Fiもある」「たくさんの展示があっておもしろい」と学生に人気。図書館、ギャラリー、会議室などを備えた複合施設。住所：日田市上城内町２−６</t>
         </is>
       </c>
+      <c r="H49" t="inlineStr"/>
+      <c r="I49" t="inlineStr"/>
+      <c r="J49" t="inlineStr"/>
+      <c r="K49" t="inlineStr"/>
+      <c r="L49" t="inlineStr"/>
+      <c r="M49" t="inlineStr"/>
+      <c r="N49" t="inlineStr"/>
+      <c r="O49" t="inlineStr"/>
+      <c r="P49" t="inlineStr"/>
+      <c r="Q49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="n">
@@ -1984,6 +2514,16 @@
           <t>【アンケート人気：11件】「日田のシンボル」「たまに路上ライブがある」と評価される日田の玄関口。観光案内所、レンタサイクルあり。豆田町へも徒歩圏内。住所：日田市元町１１－１</t>
         </is>
       </c>
+      <c r="H50" t="inlineStr"/>
+      <c r="I50" t="inlineStr"/>
+      <c r="J50" t="inlineStr"/>
+      <c r="K50" t="inlineStr"/>
+      <c r="L50" t="inlineStr"/>
+      <c r="M50" t="inlineStr"/>
+      <c r="N50" t="inlineStr"/>
+      <c r="O50" t="inlineStr"/>
+      <c r="P50" t="inlineStr"/>
+      <c r="Q50" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
